--- a/MVP-1/SRS/FlatWire_ClientQuestions.xlsx
+++ b/MVP-1/SRS/FlatWire_ClientQuestions.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions to Confirm'!$A$4:$L$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Open Questions'!$A$4:$Q$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Open Questions'!$A$4:$Q$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -59,7 +59,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +96,11 @@
         <fgColor rgb="00D9E7F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4E7EA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -123,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -156,6 +161,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -541,7 +549,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Issued August 12, 2026 · 33 open questions · 25 recorded decisions to confirm</t>
+          <t>Issued August 12, 2026 · 57 open questions · 25 recorded decisions to confirm</t>
         </is>
       </c>
     </row>
@@ -639,7 +647,7 @@
     <row r="20">
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Open questions by priority: Critical 5 · High 25 · Medium 3.</t>
+          <t>Open questions by priority: Critical 7 · High 41 · Medium 8 · Low 1.</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1560,7 @@
             <t>not</t>
           </r>
           <r>
-            <t xml:space="preserve"> commit the shared coil status, and there is </t>
+            <t xml:space="preserve"> commit the status, and there is </t>
           </r>
           <r>
             <rPr>
@@ -1563,7 +1571,40 @@
             <t>no intermediate status</t>
           </r>
           <r>
-            <t xml:space="preserve"> for a rod that has been welded but not yet checked in — you confirmed one is not needed. Rod status STAGED is the real staging status for FL1 rather than a leftover value.</t>
+            <t xml:space="preserve"> for a rod that has been welded but not yet checked in — you confirmed one is not needed. Rod status STAGED is the real staging status for FL1 rather than a leftover value. ⚠ </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Amended August 18, 2026, following your direction that there will be no changes to the existing scheduling system's database.</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> The timing you confirmed is unchanged — the status still changes at check-in and not before — but it is now recorded on the </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>flat wire module's own rod record</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, and the existing shared coil record is </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>not written at all</t>
+          </r>
+          <r>
+            <t>. Nothing about the operator's experience changes.</t>
           </r>
         </is>
       </c>
@@ -1615,7 +1656,51 @@
             <t>check-in</t>
           </r>
           <r>
-            <t xml:space="preserve"> alongside the status, so that pre-check-in has no effect outside the flat wire system at all.</t>
+            <t xml:space="preserve"> alongside the status, so that pre-check-in has no effect outside the flat wire system at all. ⚠ </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>The August 18 direction has already taken the status half of that position further than we proposed</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> — the status now never leaves the flat wire system at any point. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>One consequence needs your view, and it is the reason this question is still worth a minute of your time:</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> with nothing written to the shared coil record, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>the existing scheduling and reporting screens no longer show that a rod is on a flattening line.</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> The work-in-progress station, the requirements-summary entry and the routing start date all still say the rod has started, so most consumers are covered — but any report that filters on the </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>coil status field itself</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> will show flat wire material as untouched. Please tell us whether any report or screen you rely on does that.</t>
           </r>
         </is>
       </c>
@@ -3372,7 +3457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3404,7 +3489,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>33 questions outstanding, almost all with our recommended answer. Please complete the shaded columns. Sorted by priority.</t>
+          <t>57 questions outstanding, almost all with our recommended answer. Please complete the shaded columns. Sorted by priority.</t>
         </is>
       </c>
     </row>
@@ -3814,22 +3899,22 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q41</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Run start and machine setup</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Spool lifecycle</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Tim O., Engineering</t>
+          <t>Tim O. / Bob S.</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -3839,46 +3924,37 @@
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>Before a run starts, how do we confirm the roll gaps are actually set to what the pass schedule says? Does the operator measure each gap and enter the readings, does the machine report its own achieved gap position back to us, or does the system simply push the settings and start the run with no check? And if a gap is found out of tolerance, is a supervisor override enough to proceed, or must it be a hard stop?</t>
+          <t>You have asked for pre-check-in at FL2, so the operator can validate the next spool rather than discover at check-in that they have fetched the wrong one. We need to know what that step should actually do. Does it record that the check was made, or is it a look-and-go validation? Does it reserve the line for that spool, or release it again immediately? And must it be completed before check-in, or does it stay optional as it is on the rod line?</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>The pass schedule specifies a roll gap for every active component. When the operator acknowledges the schedule at check-in, those values are sent to the machine. Nothing currently reads back what the machine actually did with them, so a mis-sent value and a correct one look identical to the system, and the first evidence of a problem is out-of-spec wire. Whether a readback is even available differs by component, which is why this needs an engineering answer rather than a design decision.</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="n"/>
+          <t>FL2 has one payoff and no floor space, so there is nowhere to stage a spool — which is why pre-check-in was previously excluded there. Your reason for wanting it is validation rather than staging, and those are different things. Two of the things the rod line's pre-check-in does have no equivalent at FL2: it performs a visual inspection before unbanding, which is not done on a spool because the material was already inspected as rod, and it manages two alternating payoff positions, of which FL2 has one.</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>FL2 does get pre-check-in, to validate the next spool and eliminate downtime spent locating the right material after finding out at check-in that the wrong spool was collected.</t>
+        </is>
+      </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>(1) The operator physically measures each active roll gap and enters the readings; the system compares them against the pass schedule. (2) The machine reports its achieved gap position and the system compares that against the setting; the run cannot start until every active component reports within tolerance. (3) The operator acknowledges the schedule, settings are sent, and the run starts with no readback at all — the current implied design, which we rate high risk.</t>
+          <t>(1) Validate only — the screen checks the spool and records nothing. (2) Validate and record, releasing the line again immediately. (3) Validate and reserve the line until the spool is checked in. And separately, for any of the three: required before check-in, or optional.</t>
         </is>
       </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
-          <r>
-            <t xml:space="preserve">Option 2 — machine readback compared against the pass schedule setting — for every component where a readback exists, falling back to option 1 (operator measurement) on components where it does not. Please tell us which components can report their gap position. Option 3 should not ship. Treat an out-of-tolerance gap as a </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>supervisor-overridable block, not a hard stop</t>
-          </r>
-          <r>
-            <t>.</t>
-          </r>
+          <t>Option 2, and keep the step optional. Recording it makes the check auditable and means the operator's effort is not lost if they are called away. Releasing rather than reserving reflects the single payoff — a reservation would block the line on a spool that has not arrived. Keeping it optional matters most: check-in must stay reachable without it, exactly as on the rod line, so a busy operator is never prevented from starting a run.</t>
         </is>
       </c>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>A run that starts with no readback cannot tell a mis-sent setting from a correct one, and the cost of finding out is scrap. A hard stop with no override is the opposite failure: it strands the line every time the tolerance value itself turns out to be wrong.</t>
+          <t>The answer decides whether this is a change to a screen you have already seen or a new record with new rules behind it, and that difference is material to both the estimate and the sprint it lands in. It also decides whether an operator can be blocked from starting a run, which is the kind of rule that is easy to agree in a meeting and expensive to live with on a shift.</t>
         </is>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>The run-start gate cannot be built, and the check-in sequence has an unspecified step in the middle of it.</t>
+          <t>The screen can be prepared but the step itself cannot be built, and it cannot be included in the sprint starting 24 August.</t>
         </is>
       </c>
       <c r="M10" s="10" t="n"/>
@@ -3890,46 +3966,58 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q48</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Output and packaging</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Planning and scheduling</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Tim O., Shannon R.</t>
+          <t>Tim O. / Planning</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Confirmation of our reading</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Final output is two coreless oscillated coils per skid. Do skid labelling, alpha assignment and packaging records follow United Aluminum's existing coil packaging rules unchanged, or does flat wire need its own variations? And which existing convention is the one being inherited?</t>
+          <t>When planning puts two orders on a single rod, can those two orders call for different mill settings - a different gauge, width or edge - or will they always share the same settings?</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>The two-coils-per-skid rule was given to us as inherited from existing practice, but the artifacts asserting that never named a specific, definable convention to inherit from. The output geometry and the handling are the same as existing coil packaging, so we expect the rules to carry over unchanged.</t>
+          <t>A rod stays mounted across an order boundary, and the machine settings are sent to the line once, when the rod is checked in. If the second order needs different settings there is no moment at which to send them without stopping and re-checking-in, which means unloading a part-run rod.</t>
         </is>
       </c>
       <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>(1) Two orders on one rod always share the same settings, and planning enforces it. (2) They may differ, and the operator must check the rod out and back in at the boundary. (3) They may differ and the system sends new settings mid-rod.</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Option 1. Have planning refuse to pair orders with different settings on one rod.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Option 3 means changing the mill while material is in it, which nobody has proposed and which would leave a length of wire made to neither setting. Option 2 works but throws away the benefit of pairing orders on a rod in the first place. Option 1 costs planning a validation rule and costs the shopfloor nothing.</t>
+        </is>
+      </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>Label layout and packaging records cannot be finalised, and coil and skid labels are printed output.</t>
+          <t>This is the most consequential unanswered question in the rod-to-order design. If different settings are possible, the mounted-across-the-boundary flow needs a stop-and-restart path built into it, and the estimate grows.</t>
         </is>
       </c>
       <c r="M11" s="7" t="n"/>
@@ -3941,12 +4029,12 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Certification and traceability</t>
+          <t>Run start and machine setup</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -3956,7 +4044,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Tim O., Mick</t>
+          <t>Tim O., Engineering</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -3966,42 +4054,46 @@
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>What is the minimum traceability unit welding wire customers require — coil, lot or heat? Does that granularity have to be printed on the Certificate of Conformance, or is a lot reference enough?</t>
+          <t>Before a run starts, how do we confirm the roll gaps are actually set to what the pass schedule says? Does the operator measure each gap and enter the readings, does the machine report its own achieved gap position back to us, or does the system simply push the settings and start the run with no check? And if a gap is found out of tolerance, is a supervisor override enough to proceed, or must it be a hard stop?</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <r>
-            <t xml:space="preserve">We already record which source rods produced which footage of output, so a coil-level certificate can resolve down to lot or heat when asked. What we need to know is what has to be </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>printed</t>
+          <t>The pass schedule specifies a roll gap for every active component. When the operator acknowledges the schedule at check-in, those values are sent to the machine. Nothing currently reads back what the machine actually did with them, so a mis-sent value and a correct one look identical to the system, and the first evidence of a problem is out-of-spec wire. Whether a readback is even available differs by component, which is why this needs an engineering answer rather than a design decision.</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>(1) The operator physically measures each active roll gap and enters the readings; the system compares them against the pass schedule. (2) The machine reports its achieved gap position and the system compares that against the setting; the run cannot start until every active component reports within tolerance. (3) The operator acknowledges the schedule, settings are sent, and the run starts with no readback at all — the current implied design, which we rate high risk.</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Option 2 — machine readback compared against the pass schedule setting — for every component where a readback exists, falling back to option 1 (operator measurement) on components where it does not. Please tell us which components can report their gap position. Option 3 should not ship. Treat an out-of-tolerance gap as a </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>supervisor-overridable block, not a hard stop</t>
           </r>
           <r>
             <t>.</t>
           </r>
         </is>
       </c>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="inlineStr">
-        <is>
-          <t>Build coil-level traceability with full rod genealogy behind it, print the lot reference, and hold the heat detail queryable. Please confirm only whether heat must be printed.</t>
-        </is>
-      </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>The genealogy we already capture satisfies the strictest plausible answer without waiting for it, so the only real decision is what appears on the printed certificate.</t>
+          <t>A run that starts with no readback cannot tell a mis-sent setting from a correct one, and the cost of finding out is scrap. A hard stop with no override is the opposite failure: it strands the line every time the tolerance value itself turns out to be wrong.</t>
         </is>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>Certificate layout cannot be finalised. The underlying data model is unaffected either way.</t>
+          <t>The run-start gate cannot be built, and the check-in sequence has an unspecified step in the middle of it.</t>
         </is>
       </c>
       <c r="M12" s="10" t="n"/>
@@ -4013,12 +4105,12 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Certification and traceability</t>
+          <t>Output and packaging</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -4028,39 +4120,31 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Tim O.</t>
+          <t>Tim O., Shannon R.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Confirmation of our reading</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>When a weld joins two source rods into one continuous run, how is the output footage attributed between them for certification and yield — split at the weld point, or all attributed to whichever rod contributed most?</t>
+          <t>Final output is two coreless oscillated coils per skid. Do skid labelling, alpha assignment and packaging records follow United Aluminum's existing coil packaging rules unchanged, or does flat wire need its own variations? And which existing convention is the one being inherited?</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>The weld already records the footage position at which it was made, so a footage-based split needs no extra capture. Attributing the whole coil to the larger contributor would make a certificate assert that material came from a rod it did not come from.</t>
+          <t>The two-coils-per-skid rule was given to us as inherited from existing practice, but the artifacts asserting that never named a specific, definable convention to inherit from. The output geometry and the handling are the same as existing coil packaging, so we expect the rules to carry over unchanged.</t>
         </is>
       </c>
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Footage-based split at the weld point, not dominant-rod attribution.</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>It is the natural reading of data we already hold, it costs nothing extra at capture, and the alternative puts an untrue statement on a certificate.</t>
-        </is>
-      </c>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>Certificate and yield attribution for welded runs is undefined — and welded runs are the normal case on continuous feed.</t>
+          <t>Label layout and packaging records cannot be finalised, and coil and skid labels are printed output.</t>
         </is>
       </c>
       <c r="M13" s="7" t="n"/>
@@ -4072,7 +4156,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -4087,39 +4171,52 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Tim O., Sales</t>
+          <t>Tim O., Mick</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>Values or data</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>Is there a customer-specified limit on how many weld joints a single coreless oscillated coil may contain?</t>
+          <t>What is the minimum traceability unit welding wire customers require — coil, lot or heat? Does that granularity have to be printed on the Certificate of Conformance, or is a lot reference enough?</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Too many joints can jam the customer's welding equipment. If a limit exists it has to be a validation at coil completion, and validations of that kind are cheap to add now and expensive to retrofit once certificates are being issued.</t>
+          <r>
+            <t xml:space="preserve">We already record which source rods produced which footage of output, so a coil-level certificate can resolve down to lot or heat when asked. What we need to know is what has to be </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>printed</t>
+          </r>
+          <r>
+            <t>.</t>
+          </r>
         </is>
       </c>
       <c r="H14" s="10" t="n"/>
       <c r="I14" s="10" t="n"/>
       <c r="J14" s="10" t="inlineStr">
         <is>
-          <t>Build the validation now with a per-order configurable limit that defaults to unlimited, so it sits inert until Sales supplies a value per customer. A superseded weld attempt should not count toward the limit — see the related question on rework welds.</t>
+          <t>Build coil-level traceability with full rod genealogy behind it, print the lot reference, and hold the heat detail queryable. Please confirm only whether heat must be printed.</t>
         </is>
       </c>
       <c r="K14" s="10" t="inlineStr">
         <is>
-          <t>It costs little to add at completion and a great deal to add after certificates are issuing, and a null default means no behaviour changes until you give us a number.</t>
+          <t>The genealogy we already capture satisfies the strictest plausible answer without waiting for it, so the only real decision is what appears on the printed certificate.</t>
         </is>
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>No functional block, provided the validation is built now. If it is not, adding it later touches the certificate path.</t>
+          <t>Certificate layout cannot be finalised. The underlying data model is unaffected either way.</t>
         </is>
       </c>
       <c r="M14" s="10" t="n"/>
@@ -4131,7 +4228,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -4146,7 +4243,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Tim O., Mick</t>
+          <t>Tim O.</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -4156,29 +4253,29 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Are Certificates of Conformance issued per coil, per order or per heat for flat wire? Is that consistent across all flat wire customers, or customer-specific?</t>
+          <t>When a weld joins two source rods into one continuous run, how is the output footage attributed between them for certification and yield — split at the weld point, or all attributed to whichever rod contributed most?</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Finished coils are roughly 900 lb, so a 44,000 lb order is around fifty coils. Per-coil certification on that order means fifty certificates.</t>
+          <t>The weld already records the footage position at which it was made, so a footage-based split needs no extra capture. Attributing the whole coil to the larger contributor would make a certificate assert that material came from a rod it did not come from.</t>
         </is>
       </c>
       <c r="H15" s="7" t="n"/>
       <c r="I15" s="7" t="n"/>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Issue per order with per-coil detail attached, rather than separate certificates, and allow a customer-specific override. Please confirm whether any welding wire customer contractually requires per-coil.</t>
+          <t>Footage-based split at the weld point, not dominant-rod attribution.</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>It matches how the coil business already issues certificates, and it avoids fifty certificates on a single order while still carrying the per-coil detail.</t>
+          <t>It is the natural reading of data we already hold, it costs nothing extra at capture, and the alternative puts an untrue statement on a certificate.</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>Certificate issuing cannot be built.</t>
+          <t>Certificate and yield attribution for welded runs is undefined — and welded runs are the normal case on continuous feed.</t>
         </is>
       </c>
       <c r="M15" s="7" t="n"/>
@@ -4190,12 +4287,12 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Quality and tolerances</t>
+          <t>Certification and traceability</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -4205,39 +4302,39 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Tim O., Technical</t>
+          <t>Tim O., Sales</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Values or data</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>Is there a maximum allowable twist per foot for flat wire, particularly for welding wire that has to feed through automated welding equipment?</t>
+          <t>Is there a customer-specified limit on how many weld joints a single coreless oscillated coil may contain?</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Excess twist jams wire at the customer and is a common first-shipment field failure. Camber has already been settled as an optional measurement active only when the order specifies a limit; twist is the same shape of characteristic.</t>
+          <t>Too many joints can jam the customer's welding equipment. If a limit exists it has to be a validation at coil completion, and validations of that kind are cheap to add now and expensive to retrofit once certificates are being issued.</t>
         </is>
       </c>
       <c r="H16" s="10" t="n"/>
       <c r="I16" s="10" t="n"/>
       <c r="J16" s="10" t="inlineStr">
         <is>
-          <t>Treat it exactly as camber is already treated — an optional quality checkpoint field, active only when the order specifies a limit. Please supply the limit only for the customers who require it.</t>
+          <t>Build the validation now with a per-order configurable limit that defaults to unlimited, so it sits inert until Sales supplies a value per customer. A superseded weld attempt should not count toward the limit — see the related question on rework welds.</t>
         </is>
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>It reuses a pattern already agreed for a customer-conditional dimensional characteristic, needs no new mechanism, and does not make every order measure something only some orders care about.</t>
+          <t>It costs little to add at completion and a great deal to add after certificates are issuing, and a null default means no behaviour changes until you give us a number.</t>
         </is>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>Welding wire orders cannot enforce a twist limit; no impact on orders that do not specify one.</t>
+          <t>No functional block, provided the validation is built now. If it is not, adding it later touches the certificate path.</t>
         </is>
       </c>
       <c r="M16" s="10" t="n"/>
@@ -4249,12 +4346,12 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Costing and yield</t>
+          <t>Certification and traceability</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -4264,52 +4361,39 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Tim O., Margo</t>
+          <t>Tim O., Mick</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Values or data</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>Is there a per-pass scrap allowance — die entry crop, edge trim, end crop, weld scrap — that planning must apply when sizing rod input for an order?</t>
+          <t>Are Certificates of Conformance issued per coil, per order or per heat for flat wire? Is that consistent across all flat wire customers, or customer-specific?</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>If this is not built in, planners will systematically under-order rod and the shortage will be discovered at the machine.</t>
+          <t>Finished coils are roughly 900 lb, so a 44,000 lb order is around fifty coils. Per-coil certification on that order means fifty certificates.</t>
         </is>
       </c>
       <c r="H17" s="7" t="n"/>
       <c r="I17" s="7" t="n"/>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <r>
-            <t xml:space="preserve">Hold a per-pass scrap allowance as configuration, with die entry crop, edge trim, end crop and weld scrap as </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>separate line items</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> so each can be tuned independently. Seed them provisionally and refine from trial data. The figures must agree with the metallic yield answer.</t>
-          </r>
+          <t>Issue per order with per-coil detail attached, rather than separate certificates, and allow a customer-specific override. Please confirm whether any welding wire customer contractually requires per-coil.</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Rolling them into one factor makes the number impossible to improve later, because nobody can tell which component was wrong.</t>
+          <t>It matches how the coil business already issues certificates, and it avoids fifty certificates on a single order while still carrying the per-coil detail.</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>Planning under-orders rod and the shortage surfaces at the machine.</t>
+          <t>Certificate issuing cannot be built.</t>
         </is>
       </c>
       <c r="M17" s="7" t="n"/>
@@ -4321,12 +4405,12 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Rod checkout and partial material</t>
+          <t>Quality and tolerances</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
@@ -4336,43 +4420,39 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Tim O., Scott, Bob S., Shannon R.</t>
+          <t>Tim O., Technical</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>Confirmation of our reading</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>When a rod is removed part-used and later brought back, how does its history carry forward? And is a scale going to be available at the payoff to weigh the returning rod?</t>
+          <t>Is there a maximum allowable twist per foot for flat wire, particularly for welding wire that has to feed through automated welding equipment?</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Partial decisions were given in May 2026 and the carry-forward design has since been built to them. The remaining uncertainty is the scale. Our design works from an estimated remaining weight; a scale would improve the estimate's accuracy rather than change the design.</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>Any material left in the mill when the rod is removed is scrapped. A single rod can legitimately produce partial spool identifiers across several separate runs, and that capability is needed. The remaining rod going back to the warehouse may need weighing to validate remaining weight — Scott, Bob and Shannon were asked to weigh in on whether a small scale at the payoff should be available.</t>
-        </is>
-      </c>
+          <t>Excess twist jams wire at the customer and is a common first-shipment field failure. Camber has already been settled as an optional measurement active only when the order specifies a limit; twist is the same shape of characteristic.</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="n"/>
       <c r="I18" s="10" t="n"/>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>Confirm the carry-forward design as built: the rod keeps a persistent record carrying footage run to date and an estimated remaining weight, and each partial spool records the rod it came from. Treat the payoff scale as a separate question — the same scale question arises at the take-up — and do not hold the build for it.</t>
+          <t>Treat it exactly as camber is already treated — an optional quality checkpoint field, active only when the order specifies a limit. Please supply the limit only for the customers who require it.</t>
         </is>
       </c>
       <c r="K18" s="10" t="inlineStr">
         <is>
-          <t>The design already works from an estimate, so the scale answer changes accuracy rather than structure. Holding the build for it delays working functionality for an improvement.</t>
+          <t>It reuses a pattern already agreed for a customer-conditional dimensional characteristic, needs no new mechanism, and does not make every order measure something only some orders care about.</t>
         </is>
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>The carry-forward design remains unconfirmed while it is being built against. The scale answer separately affects how accurate returned-rod weights are.</t>
+          <t>Welding wire orders cannot enforce a twist limit; no impact on orders that do not specify one.</t>
         </is>
       </c>
       <c r="M18" s="10" t="n"/>
@@ -4384,12 +4464,12 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Rod checkout and partial material</t>
+          <t>Costing and yield</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -4399,47 +4479,52 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Tim O., Engineering</t>
+          <t>Tim O., Margo</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Confirmation of our reading</t>
+          <t>Values or data</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>When a rod is checked out mid-run, what should happen to the machine settings the system had sent? We have proposed a behaviour and need engineering to confirm it.</t>
+          <t>Is there a per-pass scrap allowance — die entry crop, edge trim, end crop, weld scrap — that planning must apply when sizing rod input for an order?</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>The concern is losing footage or interrupting the machine's control logic while material is still moving. Our proposal avoids both by never commanding the machine and only clearing settings once the line is confirmed stopped. Whether "stopped" is reliably readable depends on the line-state signal, which is the subject of a separate question.</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Nothing yet — the behaviour below is our proposal awaiting engineering confirmation.</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>As proposed: the application never sends a stop command — the operator always controls the machine physically; settings are cleared only when the line is confirmed stopped; and the system checks the line is stopped before allowing checkout to proceed. On screen: if the line is still running when the operator presses Check Out Rod, checkout is blocked with the message "Line is still running. Stop the line before checking out the rod." If the line is confirmed stopped, the checkout dialog opens, the footage reading is taken and locked at that moment, and settings are cleared only after the operator confirms.</t>
-        </is>
-      </c>
+          <t>If this is not built in, planners will systematically under-order rod and the shortage will be discovered at the machine.</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Adopt the proposed behaviour as written. We are asking engineering to confirm the line-state signal we read to decide "stopped", not to redesign the flow.</t>
+          <r>
+            <t xml:space="preserve">Hold a per-pass scrap allowance as configuration, with die entry crop, edge trim, end crop and weld scrap as </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>separate line items</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> so each can be tuned independently. Seed them provisionally and refine from trial data. The figures must agree with the metallic yield answer.</t>
+          </r>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>It is the only design that cannot drop footage or interrupt control logic mid-motion, because the operator stops the line physically and the system only ever follows.</t>
+          <t>Rolling them into one factor makes the number impossible to improve later, because nobody can tell which component was wrong.</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>Mid-run rod checkout cannot be built, and it is a routine operational event.</t>
+          <t>Planning under-orders rod and the shortage surfaces at the machine.</t>
         </is>
       </c>
       <c r="M19" s="7" t="n"/>
@@ -4451,12 +4536,12 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Q17</t>
+          <t>Q12</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Spool lifecycle</t>
+          <t>Rod checkout and partial material</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
@@ -4466,56 +4551,43 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Tim O.</t>
+          <t>Tim O., Scott, Bob S., Shannon R.</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Confirmation of our reading</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>What is the full list of spool statuses the system stores, and which transitions between them are valid? Separately: a spool on quality hold is currently neither ready nor checked in, so it does not appear on the FL2 queue at all — where should it show?</t>
+          <t>When a rod is removed part-used and later brought back, how does its history carry forward? And is a scale going to be available at the payoff to weigh the returning rod?</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>What the FL2 operator sees was settled on 2 August 2026, but that decision fixed the operator's view rather than what the system records, and two vocabularies for the stored status are still unreconciled. Without a defined set of valid transitions the system cannot prevent invalid progressions — a spool planned for two orders at once, or a completed spool re-opened for check-in.</t>
+          <t>Partial decisions were given in May 2026 and the carry-forward design has since been built to them. The remaining uncertainty is the scale. Our design works from an estimated remaining weight; a scale would improve the estimate's accuracy rather than change the design.</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>FL2 shows two statuses and runs one spool at a time. Because FL2 has no space to stage material, a spool is either waiting for the line or on it — the operator-visible vocabulary is "Ready for FL2" and "Checked in", with no staging status and no "at the payoff" status. Check-in is exclusive: while any spool is checked in, no spool offers a check-in action, and the action returns only on checkout. From May 2026: spools carry unique identifiers similar to furnace plates, identifiers are loaded onto a spool number at the start of the FL1 job with the operator entering the spool number used, and the spool is then tracked physically and in the system through the furnace and cooling until the FL2 operator selects it by spool number.</t>
+          <t>Any material left in the mill when the rod is removed is scrapped. A single rod can legitimately produce partial spool identifiers across several separate runs, and that capability is needed. The remaining rod going back to the warehouse may need weighing to validate remaining weight — Scott, Bob and Shannon were asked to weigh in on whether a small scale at the payoff should be available.</t>
         </is>
       </c>
       <c r="I20" s="10" t="n"/>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <r>
-            <t xml:space="preserve">Make the stored vocabulary the existing coil status set already in use across the plant, and treat the two-status FL2 view as a filtered presentation of it rather than a second vocabulary. Add a third </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>view</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> state, Held, for the quality-held spool — visible on the queue with no check-in action — so it stops being invisible.</t>
-          </r>
+          <t>Confirm the carry-forward design as built: the rod keeps a persistent record carrying footage run to date and an estimated remaining weight, and each partial spool records the rod it came from. Treat the payoff scale as a separate question — the same scale question arises at the take-up — and do not hold the build for it.</t>
         </is>
       </c>
       <c r="K20" s="10" t="inlineStr">
         <is>
-          <t>Reusing the existing status set closes the two-vocabulary problem without inventing a third list. A quality-held spool that appears nowhere is a spool nobody chases.</t>
+          <t>The design already works from an estimate, so the scale answer changes accuracy rather than structure. Holding the build for it delays working functionality for an improvement.</t>
         </is>
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>The system cannot enforce valid status progressions, and quality-held spools are invisible to the FL2 operator.</t>
+          <t>The carry-forward design remains unconfirmed while it is being built against. The scale answer separately affects how accurate returned-rod weights are.</t>
         </is>
       </c>
       <c r="M20" s="10" t="n"/>
@@ -4527,12 +4599,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Q18</t>
+          <t>Q13</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Spool lifecycle</t>
+          <t>Rod checkout and partial material</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -4542,56 +4614,47 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Tim O., Operations</t>
+          <t>Tim O., Engineering</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Confirmation of our reading</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Two parts. Which order field carries the customer's minimum and maximum weight? And if the operator does not acknowledge the completion notification and weight keeps climbing past target, should the notification escalate to a distinct over-target state, or keep showing "target reached" with a percentage above 100?</t>
+          <t>When a rod is checked out mid-run, what should happen to the machine settings the system had sent? We have proposed a behaviour and need engineering to confirm it.</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>The basis was settled on 30 July 2026 — completion is graded against the customer's weight range — but the field that carries that range has not been named, and there are two candidate sources for a target: the order's maximum spool weight, and the take-up equipment capacity. Note the customer maximum can sit well below the finished-coil take-up capacity, in which case the customer value governs rather than the equipment cap.</t>
+          <t>The concern is losing footage or interrupting the machine's control logic while material is still moving. Our proposal avoids both by never commanding the machine and only clearing settings once the line is confirmed stopped. Whether "stopped" is reliably readable depends on the line-state signal, which is the subject of a separate question.</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>The basis is the customer weight range, not a fixed default: the customer specifies a minimum and maximum — for example 900 lb maximum and 800 lb minimum — and completion is graded against that range by weight, not by footage and not against an assumed default. Spools are sized at roughly 1,800 lb so two finished coils can be cut from one spool at FL2.</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="n"/>
+          <t>Nothing yet — the behaviour below is our proposal awaiting engineering confirmation.</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>As proposed: the application never sends a stop command — the operator always controls the machine physically; settings are cleared only when the line is confirmed stopped; and the system checks the line is stopped before allowing checkout to proceed. On screen: if the line is still running when the operator presses Check Out Rod, checkout is blocked with the message "Line is still running. Stop the line before checking out the rod." If the line is confirmed stopped, the checkout dialog opens, the footage reading is taken and locked at that moment, and settings are cleared only after the operator confirms.</t>
+        </is>
+      </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <r>
-            <t xml:space="preserve">Carry the customer minimum and maximum on the </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>order</t>
-          </r>
-          <r>
-            <t>, reusing the existing maximum spool weight field for the maximum and adding a matching minimum, rather than introducing a new target record. On the second part, escalate to a distinct over-target state.</t>
-          </r>
+          <t>Adopt the proposed behaviour as written. We are asking engineering to confirm the line-state signal we read to decide "stopped", not to redesign the flow.</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>The short-close rule already grades against the same range, so one source serves both. A percentage climbing past 100 with no change of state gives the operator nothing new to react to at exactly the moment the equipment limit is being approached.</t>
+          <t>It is the only design that cannot drop footage or interrupt control logic mid-motion, because the operator stops the line physically and the system only ever follows.</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>The completion alert has no confirmed target to compare against, and the over-target behaviour is unspecified.</t>
+          <t>Mid-run rod checkout cannot be built, and it is a routine operational event.</t>
         </is>
       </c>
       <c r="M21" s="7" t="n"/>
@@ -4603,12 +4666,12 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Q21</t>
+          <t>Q17</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Machine interface</t>
+          <t>Spool lifecycle</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
@@ -4618,81 +4681,59 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Engineering, Tim O.</t>
+          <t>Tim O.</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>Values or data</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>Three specifics about the signal the machine uses to report whether a line is running. First and most important: what are the actual state values it reports — is it a simple running/stopped indication, or does it distinguish running, stopped, paused, faulted, threading and jogging? Second: how long must "stopped" persist before we treat the stop as real? Third: if the operator has already used the software pause dialog and given a reason, should the stop-confirmation prompt be suppressed?</t>
+          <t>What is the full list of spool statuses the system stores, and which transitions between them are valid? Separately: a spool on quality hold is currently neither ready nor checked in, so it does not appear on the FL2 queue at all — where should it show?</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>This signal is what tells the system a spool can be removed and a rod can be checked out. If a threading or jogging state reports as "stopped", the system will offer those actions while the machine is still moving — so we need the literal list of values, not a description of them.</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="n"/>
+          <t>What the FL2 operator sees was settled on 2 August 2026, but that decision fixed the operator's view rather than what the system records, and two vocabularies for the stored status are still unreconciled. Without a defined set of valid transitions the system cannot prevent invalid progressions — a spool planned for two orders at once, or a completed spool re-opened for check-in.</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>FL2 shows two statuses and runs one spool at a time. Because FL2 has no space to stage material, a spool is either waiting for the line or on it — the operator-visible vocabulary is "Ready for FL2" and "Checked in", with no staging status and no "at the payoff" status. Check-in is exclusive: while any spool is checked in, no spool offers a check-in action, and the action returns only on checkout. From May 2026: spools carry unique identifiers similar to furnace plates, identifiers are loaded onto a spool number at the start of the FL1 job with the operator entering the spool number used, and the spool is then tracked physically and in the system through the furnace and cooling until the FL2 operator selects it by spool number.</t>
+        </is>
+      </c>
       <c r="I22" s="10" t="n"/>
       <c r="J22" s="10" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">On the first point, please give us the enumeration as a </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>list of literal values</t>
-          </r>
-          <r>
-            <t xml:space="preserve">, because the filtering depends on whether threading and jogging report distinctly or as stopped. On the second and third, adopt our proposals: a </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>five-second dwell</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> with speed at approximately zero as corroboration, and </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>suppress the prompt when a pause reason has already been captured</t>
-          </r>
-          <r>
-            <t>, unless that reason indicates spool removal.</t>
+            <t xml:space="preserve">Make the stored vocabulary the existing coil status set already in use across the plant, and treat the two-status FL2 view as a filtered presentation of it rather than a second vocabulary. Add a third </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>view</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> state, Held, for the quality-held spool — visible on the queue with no check-in action — so it stops being invisible.</t>
           </r>
         </is>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t>Only the first point genuinely needs your input — the other two are defaults we are happy to be corrected on. A described vocabulary rather than a literal one is what leaves us guessing.</t>
+          <t>Reusing the existing status set closes the two-vocabulary problem without inventing a third list. A quality-held spool that appears nowhere is a spool nobody chases.</t>
         </is>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>The spool-removal prompt and the rod-checkout gate both depend on deciding when the line is really stopped, so neither can be built.</t>
-        </is>
-      </c>
-      <c r="M22" s="10" t="inlineStr">
-        <is>
-          <t>Q13, Q27</t>
-        </is>
-      </c>
+          <t>The system cannot enforce valid status progressions, and quality-held spools are invisible to the FL2 operator.</t>
+        </is>
+      </c>
+      <c r="M22" s="10" t="n"/>
       <c r="N22" s="8" t="n"/>
       <c r="O22" s="8" t="n"/>
       <c r="P22" s="8" t="n"/>
@@ -4701,12 +4742,12 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Q22</t>
+          <t>Q18</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Quality and tolerances</t>
+          <t>Spool lifecycle</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -4716,56 +4757,56 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Tim O.</t>
+          <t>Tim O., Operations</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Values or data</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>We need the actual tolerance figures. The shape was confirmed on 30 July 2026 — upper and lower limits for gauge, width, diameter and ovality — and the values were to follow by e-mail. They have not arrived. Two secondary points: are the alloy tolerance figures already in circulation authoritative or do they need Process Engineering sign-off, and can tolerance vary by rod vendor or by nominal size within one alloy?</t>
+          <t>Two parts. Which order field carries the customer's minimum and maximum weight? And if the operator does not acknowledge the completion notification and weight keeps climbing past target, should the notification escalate to a distinct over-target state, or keep showing "target reached" with a percentage above 100?</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Incoming rod diameter has to be validated against nominal plus or minus a tolerance at both pre-check-in and check-in, and there is currently nowhere to read that tolerance from. In the interim the pre-check-in screen shows a per-alloy set of figures that is explicitly mock data with nothing behind it. We are holding the reference data empty rather than seeding a guess: "plus or minus ten" is not a specification, and a seeded wrong number is worse than an empty one because it looks authoritative. Note the figures in circulation are tighter than the placeholder in the mockup, which means out-of-tolerance rod would have been accepted.</t>
+          <t>The basis was settled on 30 July 2026 — completion is graded against the customer's weight range — but the field that carries that range has not been named, and there are two candidate sources for a target: the order's maximum spool weight, and the take-up equipment capacity. Note the customer maximum can sit well below the finished-coil take-up capacity, in which case the customer value governs rather than the equipment cap.</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>The tolerances exist, they are minimum and maximum pairs rather than single values, and there are four of them — gauge, width, diameter and ovality. They live in reference data and are applied at both pre-check-in and check-in.</t>
+          <t>The basis is the customer weight range, not a fixed default: the customer specifies a minimum and maximum — for example 900 lb maximum and 800 lb minimum — and completion is graded against that range by weight, not by footage and not against an assumed default. Spools are sized at roughly 1,800 lb so two finished coils can be cut from one spool at FL2.</t>
         </is>
       </c>
       <c r="I23" s="7" t="n"/>
       <c r="J23" s="7" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Send the four sets of figures. We will make the structural change now and seed nothing until they arrive, so the build is not waiting on the values. </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Per-alloy is sufficient granularity</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> unless Process Engineering states that tolerance varies by vendor or by nominal size — please confirm that specifically. We will also consolidate the one ovality limit that is currently hard-coded so ovality is validated in one place rather than two.</t>
+            <t xml:space="preserve">Carry the customer minimum and maximum on the </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>order</t>
+          </r>
+          <r>
+            <t>, reusing the existing maximum spool weight field for the maximum and adding a matching minimum, rather than introducing a new target record. On the second part, escalate to a distinct over-target state.</t>
           </r>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>The shape is decided and the structure can be built empty, so the numbers and the schema are not blocking each other. But nothing can be validated against a tolerance that does not exist, so the figures block the check-in build regardless.</t>
+          <t>The short-close rule already grades against the same range, so one source serves both. A percentage climbing past 100 with no change of state gives the operator nothing new to react to at exactly the moment the equipment limit is being approached.</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>Rod acceptance validation at both pre-check-in and check-in cannot be completed. This is a current blocker.</t>
+          <t>The completion alert has no confirmed target to compare against, and the over-target behaviour is unspecified.</t>
         </is>
       </c>
       <c r="M23" s="7" t="n"/>
@@ -4777,12 +4818,12 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Q23</t>
+          <t>Q21</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Rod staging and pre-check-in</t>
+          <t>Machine interface</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -4792,96 +4833,81 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Tim O., IT</t>
+          <t>Engineering, Tim O.</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>Confirmation of our reading</t>
+          <t>Values or data</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <r>
-            <t xml:space="preserve">One point remains. When a staging inspection fails, should the inspector's notes be </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>mandatory</t>
-          </r>
-          <r>
-            <t>? They are currently optional but documented as expected whenever any item fails.</t>
-          </r>
+          <t>Three specifics about the signal the machine uses to report whether a line is running. First and most important: what are the actual state values it reports — is it a simple running/stopped indication, or does it distinguish running, stopped, paused, faulted, threading and jogging? Second: how long must "stopped" persist before we treat the stop as real? Third: if the operator has already used the software pause dialog and given a reason, should the stop-confirmation prompt be suppressed?</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>The substantive parts of this question were settled in July 2026. The reasoning behind them is physical: bundles are not unbanded until they are positioned at the payoff — which is precisely why the inspection happens at staging — so a rod that fails inspection is already sitting on the bay. Recording nothing left the system reporting an occupied bay as empty and offering it to the next rod, while a physically present rejected bundle blocked it.</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">A blocked bay is a </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>derived</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> state — staged, with any inspection item failed — rather than a separate status. Pre-check-in commits the staging record </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>before</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> the inspection gate, so the failure and the observation are both persisted and the bay correctly reads as blocked. There is no bypass: rejection remains the only forward path. A failed inspection is captured as a rejection on the rejection screen, the operator enters the reason there, the rod goes to hold, and that rejection is what releases the bay.</t>
-          </r>
-        </is>
-      </c>
+          <t>This signal is what tells the system a spool can be removed and a rod can be checked out. If a threading or jogging state reports as "stopped", the system will offer those actions while the machine is still moving — so we need the literal list of values, not a description of them.</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="10" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Make the inspection notes </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>mandatory when any inspection item fails</t>
-          </r>
-          <r>
-            <t>, matching the treatment already applied to the other conditional field groups.</t>
+            <t xml:space="preserve">On the first point, please give us the enumeration as a </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>list of literal values</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, because the filtering depends on whether threading and jogging report distinctly or as stopped. On the second and third, adopt our proposals: a </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>five-second dwell</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> with speed at approximately zero as corroboration, and </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>suppress the prompt when a pause reason has already been captured</t>
+          </r>
+          <r>
+            <t>, unless that reason indicates spool removal.</t>
           </r>
         </is>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t>A failure with no observation is the one case where the note carries the whole evidentiary value — and the existing documentation already says a note is expected there.</t>
+          <t>Only the first point genuinely needs your input — the other two are defaults we are happy to be corrected on. A described vocabulary rather than a literal one is what leaves us guessing.</t>
         </is>
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>Failed inspections may be recorded with no observation, which undermines the rejection audit trail.</t>
-        </is>
-      </c>
-      <c r="M24" s="10" t="n"/>
+          <t>The spool-removal prompt and the rod-checkout gate both depend on deciding when the line is really stopped, so neither can be built.</t>
+        </is>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>Q13, Q27</t>
+        </is>
+      </c>
       <c r="N24" s="8" t="n"/>
       <c r="O24" s="8" t="n"/>
       <c r="P24" s="8" t="n"/>
@@ -4890,12 +4916,12 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Q24</t>
+          <t>Q22</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Rod staging and pre-check-in</t>
+          <t>Quality and tolerances</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -4905,63 +4931,59 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Tim O., Shannon R.</t>
+          <t>Tim O.</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Values or data</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Does the same out-of-sequence supervisor override apply at check-in as well as pre-check-in? And the out-of-sequence override itself was left in place provisionally pending your review — please confirm or remove it.</t>
+          <t>We need the actual tolerance figures. The shape was confirmed on 30 July 2026 — upper and lower limits for gauge, width, diameter and ovality — and the values were to follow by e-mail. They have not arrived. Two secondary points: are the alloy tolerance figures already in circulation authoritative or do they need Process Engineering sign-off, and can tolerance vary by rod vendor or by nominal size within one alloy?</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Two parts of this were settled on 30 July 2026. On the out-of-sequence override you said it "might not be a bad idea" and asked to leave it in place while you reviewed something in the specification it may support — so it is currently built on an unconfirmed rule, and anything depending on it is depending on a provisional decision. On the check-in point, the decision said pre-check-in and check-in, but only the pre-check-in screen carries the control today.</t>
+          <t>Incoming rod diameter has to be validated against nominal plus or minus a tolerance at both pre-check-in and check-in, and there is currently nowhere to read that tolerance from. In the interim the pre-check-in screen shows a per-alloy set of figures that is explicitly mock data with nothing behind it. We are holding the reference data empty rather than seeding a guess: "plus or minus ten" is not a specification, and a seeded wrong number is worse than an empty one because it looks authoritative. Note the figures in circulation are tighter than the placeholder in the mockup, which means out-of-tolerance rod would have been accepted.</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Off-schedule is not a deviation at all — there is no blocking message and no override, and the system selects the correct station automatically. If the rod is planned for FL3 and the operator is on the FL1 tab, the screen switches to FL3 and the transaction continues, at both pre-check-in and check-in. Separately, and provisionally: the operator must be notified when the rod being checked in is not the one planning expects next, and a supervisor override is required to depart from the planned sequence — reason, badge or identifier and PIN, with a remote-approval fallback, all recorded. "Expects next" means the lowest planned sequence still available, so a blocked bundle does not freeze the sequence behind it.</t>
+          <t>The tolerances exist, they are minimum and maximum pairs rather than single values, and there are four of them — gauge, width, diameter and ovality. They live in reference data and are applied at both pre-check-in and check-in.</t>
         </is>
       </c>
       <c r="I25" s="7" t="n"/>
       <c r="J25" s="7" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Yes to the check-in point — build the identical control at check-in, because a validation enforced at one of two entry points is not enforced. Validate the PIN against the </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>existing login and authorisation service</t>
-          </r>
-          <r>
-            <t>, so one credential path serves this override, the weight-variance override and the welded pre-check-out override. And please close the review you committed to on the out-of-sequence override.</t>
+            <t xml:space="preserve">Send the four sets of figures. We will make the structural change now and seed nothing until they arrive, so the build is not waiting on the values. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Per-alloy is sufficient granularity</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> unless Process Engineering states that tolerance varies by vendor or by nominal size — please confirm that specifically. We will also consolidate the one ovality limit that is currently hard-coded so ovality is validated in one place rather than two.</t>
           </r>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>The multi-order sequencing rule independently requires the same control at check-in, so the two land together. A second credential store is an authentication surface with no owner. And a provisional rule that downstream work treats as final is the kind of thing that surfaces late.</t>
+          <t>The shape is decided and the structure can be built empty, so the numbers and the schema are not blocking each other. But nothing can be validated against a tolerance that does not exist, so the figures block the check-in build regardless.</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>The sequence validation is enforceable at only one of the two entry points, and three supervisor overrides have no confirmed credential source.</t>
-        </is>
-      </c>
-      <c r="M25" s="7" t="inlineStr">
-        <is>
-          <t>Q73</t>
-        </is>
-      </c>
+          <t>Rod acceptance validation at both pre-check-in and check-in cannot be completed. This is a current blocker.</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="n"/>
       <c r="N25" s="8" t="n"/>
       <c r="O25" s="8" t="n"/>
       <c r="P25" s="8" t="n"/>
@@ -4970,7 +4992,7 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Q25</t>
+          <t>Q23</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -4985,76 +5007,93 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Tim O., Shannon R.</t>
+          <t>Tim O., IT</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Confirmation of our reading</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>Three parts. Is running unscheduled material a real case — an unscheduled job, a trial, a rush piece the floor is told to run before planning catches up — or is planning always ahead of the floor? If it is allowed, is a supervisor override the right gate, and does it apply at both pre-check-in and check-in? And what order does the run book against: is scheduling corrected after the fact, or does the run carry an unscheduled marker?</t>
+          <r>
+            <t xml:space="preserve">One point remains. When a staging inspection fails, should the inspector's notes be </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>mandatory</t>
+          </r>
+          <r>
+            <t>? They are currently optional but documented as expected whenever any item fails.</t>
+          </r>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <r>
-            <t xml:space="preserve">The case where a rod's order is booked on the </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <i val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>other</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> rod line is settled — the station switches automatically. This is the different case where the order is booked on </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>no flattening line at all</t>
-          </r>
-          <r>
-            <t>. Today that is a refusal by omission rather than by decision: staging checks a planning allocation exists and scheduling then supplies the line, and nothing states what to do when the allocation exists but the booking does not. This was raised on the 30 July call and not reached — it was carried forward to the next session.</t>
-          </r>
-        </is>
-      </c>
-      <c r="H26" s="10" t="n"/>
+          <t>The substantive parts of this question were settled in July 2026. The reasoning behind them is physical: bundles are not unbanded until they are positioned at the payoff — which is precisely why the inspection happens at staging — so a rod that fails inspection is already sitting on the bay. Recording nothing left the system reporting an occupied bay as empty and offering it to the next rod, while a physically present rejected bundle blocked it.</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">A blocked bay is a </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>derived</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> state — staged, with any inspection item failed — rather than a separate status. Pre-check-in commits the staging record </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>before</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> the inspection gate, so the failure and the observation are both persisted and the bay correctly reads as blocked. There is no bypass: rejection remains the only forward path. A failed inspection is captured as a rejection on the rejection screen, the operator enters the reason there, the rod goes to hold, and that rejection is what releases the bay.</t>
+          </r>
+        </is>
+      </c>
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="10" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Allow it behind a supervisor override, at both pre-check-in and check-in, with the run carrying an </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>unscheduled marker</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> rather than being force-fitted to an order.</t>
+            <t xml:space="preserve">Make the inspection notes </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>mandatory when any inspection item fails</t>
+          </r>
+          <r>
+            <t>, matching the treatment already applied to the other conditional field groups.</t>
           </r>
         </is>
       </c>
       <c r="K26" s="10" t="inlineStr">
         <is>
-          <t>Trials and rush pieces are real, and a refusal by omission means the floor works around the system instead of in it. Reusing the existing supervisor override fields and adding only the marker is a far smaller change than the alternative.</t>
+          <t>A failure with no observation is the one case where the note carries the whole evidentiary value — and the existing documentation already says a note is expected there.</t>
         </is>
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>Unscheduled material cannot be run at all, and nobody has decided that it should not be.</t>
+          <t>Failed inspections may be recorded with no observation, which undermines the rejection audit trail.</t>
         </is>
       </c>
       <c r="M26" s="10" t="n"/>
@@ -5066,12 +5105,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Q26</t>
+          <t>Q24</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Shopfloor screens</t>
+          <t>Rod staging and pre-check-in</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -5081,7 +5120,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Tim O., Charles, Juan</t>
+          <t>Tim O., Shannon R.</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -5091,45 +5130,53 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Will the flat wire screens run on the same 1280×1024 monitors United Aluminum stocks today, or on 1920×1080 panels? We need this confirmed in writing, and it is time-critical.</t>
+          <t>Does the same out-of-sequence supervisor override apply at check-in as well as pre-check-in? And the out-of-sequence override itself was left in place provisionally pending your review — please confirm or remove it.</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <r>
-            <t xml:space="preserve">Every screen is designed at 1280×1024, and the minimum text size for arm's-length reading on the floor is calibrated to that. You expected the same monitors as the current screens and were going to verify with Charles and Juan; our action was to send you the required resolution by e-mail. The reason it is urgent rather than merely open: 1920×1080 is a 1.5 times width change with almost no extra height, so it is a </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>re-layout of all twenty-five-plus screens, not a rescale</t>
-          </r>
-          <r>
-            <t>. The canvas size is an acceptance criterion for the first delivery phase, which closes on 14 August 2026 — an answer after that is an answer that arrives too late to be free.</t>
-          </r>
-        </is>
-      </c>
-      <c r="H27" s="7" t="n"/>
+          <t>Two parts of this were settled on 30 July 2026. On the out-of-sequence override you said it "might not be a bad idea" and asked to leave it in place while you reviewed something in the specification it may support — so it is currently built on an unconfirmed rule, and anything depending on it is depending on a provisional decision. On the check-in point, the decision said pre-check-in and check-in, but only the pre-check-in screen carries the control today.</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Off-schedule is not a deviation at all — there is no blocking message and no override, and the system selects the correct station automatically. If the rod is planned for FL3 and the operator is on the FL1 tab, the screen switches to FL3 and the transaction continues, at both pre-check-in and check-in. Separately, and provisionally: the operator must be notified when the rod being checked in is not the one planning expects next, and a supervisor override is required to depart from the planned sequence — reason, badge or identifier and PIN, with a remote-approval fallback, all recorded. "Expects next" means the lowest planned sequence still available, so a blocked bundle does not freeze the sequence behind it.</t>
+        </is>
+      </c>
       <c r="I27" s="7" t="n"/>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>Hold 1280×1024, and confirm it in writing before 14 August. Our screens already degrade gracefully onto a wider panel — they never scale up beyond their natural size and they widen to fill available width — so 1920×1080 hardware would display them correctly today, simply leaving horizontal space unused.</t>
+          <r>
+            <t xml:space="preserve">Yes to the check-in point — build the identical control at check-in, because a validation enforced at one of two entry points is not enforced. Validate the PIN against the </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>existing login and authorisation service</t>
+          </r>
+          <r>
+            <t>, so one credential path serves this override, the weight-variance override and the welded pre-check-out override. And please close the review you committed to on the out-of-sequence override.</t>
+          </r>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>That makes 1280×1024 the safe commitment and any later re-layout an optimisation rather than a rescue. We are not re-authoring anything until this is answered.</t>
+          <t>The multi-order sequencing rule independently requires the same control at check-in, so the two land together. A second credential store is an authentication surface with no owner. And a provisional rule that downstream work treats as final is the kind of thing that surfaces late.</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>A late answer of 1920×1080 turns into a re-layout of every screen after the first phase gate has closed.</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="n"/>
+          <t>The sequence validation is enforceable at only one of the two entry points, and three supervisor overrides have no confirmed credential source.</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>Q73</t>
+        </is>
+      </c>
       <c r="N27" s="8" t="n"/>
       <c r="O27" s="8" t="n"/>
       <c r="P27" s="8" t="n"/>
@@ -5138,12 +5185,12 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Q27</t>
+          <t>Q25</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Machine interface</t>
+          <t>Rod staging and pre-check-in</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -5153,7 +5200,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Tim O., Engineering</t>
+          <t>Tim O., Shannon R.</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -5163,36 +5210,36 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <r>
-            <t xml:space="preserve">When the pass schedule's line speed is sent to the machine at check-in acknowledgement, does the machine expect it as a </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>speed setpoint</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> it should run at, or as a </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>ceiling</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> bounding whatever speed the operator selects?</t>
-          </r>
+          <t>Three parts. Is running unscheduled material a real case — an unscheduled job, a trial, a rush piece the floor is told to run before planning catches up — or is planning always ahead of the floor? If it is allowed, is a supervisor override the right gate, and does it apply at both pre-check-in and check-in? And what order does the run book against: is scheduling corrected after the fact, or does the run carry an unscheduled marker?</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Our own delivered documents say both, in different places, and they are not the same thing and do not fail the same way. If the value goes to a setpoint when the machine expected a ceiling, acknowledging a check-in starts the line moving at the scheduled speed — a serious surprise on a line that needs threading first. If it goes to a ceiling when the machine expected a setpoint, the line does not move at all and the fault looks like a missing signal. This is not resolvable from documents; it needs a controls answer.</t>
+          <r>
+            <t xml:space="preserve">The case where a rod's order is booked on the </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>other</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> rod line is settled — the station switches automatically. This is the different case where the order is booked on </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>no flattening line at all</t>
+          </r>
+          <r>
+            <t>. Today that is a refusal by omission rather than by decision: staging checks a planning allocation exists and scheduling then supplies the line, and nothing states what to do when the allocation exists but the booking does not. This was raised on the 30 July call and not reached — it was carried forward to the next session.</t>
+          </r>
         </is>
       </c>
       <c r="H28" s="10" t="n"/>
@@ -5200,36 +5247,32 @@
       <c r="J28" s="10" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Please tell us which the machine expects. Until then we will implement against a </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>ceiling</t>
-          </r>
-          <r>
-            <t>, and leave the contradictory requirement wording unfixed rather than guess.</t>
+            <t xml:space="preserve">Allow it behind a supervisor override, at both pre-check-in and check-in, with the run carrying an </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>unscheduled marker</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> rather than being force-fitted to an order.</t>
           </r>
         </is>
       </c>
       <c r="K28" s="10" t="inlineStr">
         <is>
-          <t>We prefer the loud failure. A ceiling that should have been a setpoint means the line does not move, which is obvious and safe. A setpoint that should have been a ceiling starts a threading line at full scheduled speed the moment the operator acknowledges — a commissioning-time safety surprise.</t>
+          <t>Trials and rush pieces are real, and a refusal by omission means the floor works around the system instead of in it. Reusing the existing supervisor override fields and adding only the marker is a far smaller change than the alternative.</t>
         </is>
       </c>
       <c r="L28" s="10" t="inlineStr">
         <is>
-          <t>One of the values sent at every check-in has an unconfirmed meaning, with a safety consequence in one of the two readings.</t>
-        </is>
-      </c>
-      <c r="M28" s="10" t="inlineStr">
-        <is>
-          <t>Q21, Q28, Q29</t>
-        </is>
-      </c>
+          <t>Unscheduled material cannot be run at all, and nobody has decided that it should not be.</t>
+        </is>
+      </c>
+      <c r="M28" s="10" t="n"/>
       <c r="N28" s="8" t="n"/>
       <c r="O28" s="8" t="n"/>
       <c r="P28" s="8" t="n"/>
@@ -5238,12 +5281,12 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Q28</t>
+          <t>Q26</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Machine interface</t>
+          <t>Shopfloor screens</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -5253,7 +5296,7 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Tim O., Engineering</t>
+          <t>Tim O., Charles, Juan</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -5263,49 +5306,45 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>Two parts. Is edge type actually sent to the machine at check-in — our documents list it in four places and omit it in a fifth? And do the FM2 edgers have addressable signals at all? We have found none. Separately, if an edger blade profile is to be sent, what are the permitted profile values and who maintains them?</t>
+          <t>Will the flat wire screens run on the same 1280×1024 monitors United Aluminum stocks today, or on 1920×1080 panels? We need this confirmed in writing, and it is time-critical.</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>The likely explanation for the omission is that the fifth list was written FL1-first, and FL1 has no edger — but that is our inference, not a confirmation. The more substantive finding is that no edger signal exists anywhere in the published machine interface: the only edger-adjacent signal on any line is on FL1, the one line with no edger. So the specification currently sends an edge configuration to equipment that has nothing addressable on the read side. We have proposed signal names derived from the naming convention so there is something concrete to confirm or correct, and they are marked as our invention.</t>
+          <r>
+            <t xml:space="preserve">Every screen is designed at 1280×1024, and the minimum text size for arm's-length reading on the floor is calibrated to that. You expected the same monitors as the current screens and were going to verify with Charles and Juan; our action was to send you the required resolution by e-mail. The reason it is urgent rather than merely open: 1920×1080 is a 1.5 times width change with almost no extra height, so it is a </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>re-layout of all twenty-five-plus screens, not a rescale</t>
+          </r>
+          <r>
+            <t>. The canvas size is an acceptance criterion for the first delivery phase, which closes on 14 August 2026 — an answer after that is an answer that arrives too late to be free.</t>
+          </r>
         </is>
       </c>
       <c r="H29" s="7" t="n"/>
       <c r="I29" s="7" t="n"/>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <r>
-            <t xml:space="preserve">Push edge type on </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>FL2 and FL3 only</t>
-          </r>
-          <r>
-            <t>, and treat its absence from the fifth list as the FL1-first omission it appears to be — FL1 has no edger, so there is nothing to write there. We will put our proposed edger signal names to your controls engineer as concrete strings to confirm or correct, clearly marked as our invention. Please answer the blade-profile vocabulary in the same conversation.</t>
-          </r>
+          <t>Hold 1280×1024, and confirm it in writing before 14 August. Our screens already degrade gracefully onto a wider panel — they never scale up beyond their natural size and they widen to fill available width — so 1920×1080 hardware would display them correctly today, simply leaving horizontal space unused.</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>A profile signal whose permitted values are unknown cannot be commissioned, so the paths and the vocabulary have to be settled together.</t>
+          <t>That makes 1280×1024 the safe commitment and any later re-layout an optimisation rather than a rescue. We are not re-authoring anything until this is answered.</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>Edge configuration cannot be sent to FM2, which affects every FL2 and FL3 run.</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t>Q27</t>
-        </is>
-      </c>
+          <t>A late answer of 1920×1080 turns into a re-layout of every screen after the first phase gate has closed.</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="n"/>
       <c r="N29" s="8" t="n"/>
       <c r="O29" s="8" t="n"/>
       <c r="P29" s="8" t="n"/>
@@ -5314,7 +5353,7 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Q29</t>
+          <t>Q27</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -5339,25 +5378,36 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>On a hybrid FL3 run, is the finishing mill reached through FL2's controller, or does FL3 have its own address space for it? Put plainly: when FL3 sends its settings in one batch, does that batch cross a controller boundary?</t>
+          <r>
+            <t xml:space="preserve">When the pass schedule's line speed is sent to the machine at check-in acknowledgement, does the machine expect it as a </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>speed setpoint</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> it should run at, or as a </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>ceiling</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> bounding whatever speed the operator selects?</t>
+          </r>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <r>
-            <t xml:space="preserve">Every published machine map addresses the finishing mill stands under FL2. FL3 is the hybrid route and needs both mills configured, sent as a single batch on one acknowledgement. So either the finishing mill is physically owned by the FL2 controller and FL3 reaches it through FL2's address space — in which case the FL3 send writes to </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>two controllers</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> in one logical batch — or FL3 has its own address space for it and the send is one controller.</t>
-          </r>
+          <t>Our own delivered documents say both, in different places, and they are not the same thing and do not fail the same way. If the value goes to a setpoint when the machine expected a ceiling, acknowledging a check-in starts the line moving at the scheduled speed — a serious surprise on a line that needs threading first. If it goes to a ceiling when the machine expected a setpoint, the line does not move at all and the fault looks like a missing signal. This is not resolvable from documents; it needs a controls answer.</t>
         </is>
       </c>
       <c r="H30" s="10" t="n"/>
@@ -5365,34 +5415,34 @@
       <c r="J30" s="10" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">We will assume the finishing mill is owned by the FL2 controller and that FL3 reaches it through FL2's address space, and </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>design the FL3 send for two controllers from the start</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> — a per-controller batch with an explicit compensating clear on partial failure. Please confirm or correct.</t>
+            <t xml:space="preserve">Please tell us which the machine expects. Until then we will implement against a </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>ceiling</t>
+          </r>
+          <r>
+            <t>, and leave the contradictory requirement wording unfixed rather than guess.</t>
           </r>
         </is>
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>That is the harder of the two cases, and building for it costs little now whereas discovering it at commissioning costs a redesign of the send. It also decides what a partial failure looks like and what the compensating clear has to undo — which is not a naming preference.</t>
+          <t>We prefer the loud failure. A ceiling that should have been a setpoint means the line does not move, which is obvious and safe. A setpoint that should have been a ceiling starts a threading line at full scheduled speed the moment the operator acknowledges — a commissioning-time safety surprise.</t>
         </is>
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>The hybrid send is designed against an assumption about controller ownership, and the existing commissioning test passes either way so it cannot detect a wrong guess.</t>
+          <t>One of the values sent at every check-in has an unconfirmed meaning, with a safety consequence in one of the two readings.</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr">
         <is>
-          <t>Q27</t>
+          <t>Q21, Q28, Q29</t>
         </is>
       </c>
       <c r="N30" s="8" t="n"/>
@@ -5403,12 +5453,12 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Q30</t>
+          <t>Q28</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Weights and measurement</t>
+          <t>Machine interface</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -5418,7 +5468,7 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Tim O., Bob S., Engineering</t>
+          <t>Tim O., Engineering</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -5428,49 +5478,12 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <r>
-            <t xml:space="preserve">Are there load cells on the take-ups? And is the spool completion weight </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>read</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> from them or </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>derived</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> from the footage counter and the measured cross-section? If both exist, which is authoritative when they disagree?</t>
-          </r>
+          <t>Two parts. Is edge type actually sent to the machine at check-in — our documents list it in four places and omit it in a fifth? And do the FM2 edgers have addressable signals at all? We have found none. Separately, if an edger blade profile is to be sent, what are the permitted profile values and who maintains them?</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <r>
-            <t xml:space="preserve">Two of our documents disagree. One records an assumption that load cells are fitted on both payoff positions and on both take-ups; the other states the completion weight is derived from live footage and measured cross-section. And no take-up weight signal appears in the machine interface on any line. So the interface currently specifies a behaviour — the machine-stop prompt fires when take-up weight reaches target, and the recorded value is what appears on the </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>printed label</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> — that reads a value with no published source.</t>
-          </r>
+          <t>The likely explanation for the omission is that the fifth list was written FL1-first, and FL1 has no edger — but that is our inference, not a confirmation. The more substantive finding is that no edger signal exists anywhere in the published machine interface: the only edger-adjacent signal on any line is on FL1, the one line with no edger. So the specification currently sends an edge configuration to equipment that has nothing addressable on the read side. We have proposed signal names derived from the naming convention so there is something concrete to confirm or correct, and they are marked as our invention.</t>
         </is>
       </c>
       <c r="H31" s="7" t="n"/>
@@ -5478,45 +5491,34 @@
       <c r="J31" s="7" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Specify the completion weight as </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>derived from footage and cross-section</t>
-          </r>
-          <r>
-            <t xml:space="preserve">, and treat any take-up load cell as a </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>corroborating</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> reading rather than the source. If the cells exist, tell us and we will add their signals so commissioning can read them — but the transaction will not depend on them.</t>
+            <t xml:space="preserve">Push edge type on </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>FL2 and FL3 only</t>
+          </r>
+          <r>
+            <t>, and treat its absence from the fifth list as the FL1-first omission it appears to be — FL1 has no edger, so there is nothing to write there. We will put our proposed edger signal names to your controls engineer as concrete strings to confirm or correct, clearly marked as our invention. Please answer the blade-profile vocabulary in the same conversation.</t>
           </r>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>It puts the scale-versus-calculated reconciliation in one place, one level down, instead of creating two competing rules at this level. Note the consequence: if the weight is derived, its accuracy rests entirely on the footage-to-weight dimensional basis, which is separately open and already critical.</t>
+          <t>A profile signal whose permitted values are unknown cannot be commissioned, so the paths and the vocabulary have to be settled together.</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>The most consequential number in the completion transaction — the one printed on the label — has no confirmed source.</t>
+          <t>Edge configuration cannot be sent to FM2, which affects every FL2 and FL3 run.</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Q27</t>
         </is>
       </c>
       <c r="N31" s="8" t="n"/>
@@ -5527,12 +5529,12 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Q31</t>
+          <t>Q29</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Rod checkout and partial material</t>
+          <t>Machine interface</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
@@ -5542,7 +5544,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>Tim O., Shannon R.</t>
+          <t>Tim O., Engineering</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -5552,60 +5554,62 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>Four points remain on the no-weld wire break. Is the disposition list exactly the Z-mill set — return to warehouse, scrap, continue processing, hold, concession — and does it reuse the existing screen? Is the supervisor gate a credential block, or an operator decision recorded against a supervisor's name? Does the concession path reuse the existing coil-break e-mail flow? And, before any of that, how often does this actually happen?</t>
+          <t>On a hybrid FL3 run, is the finishing mill reached through FL2's controller, or does FL3 have its own address space for it? Put plainly: when FL3 sends its settings in one batch, does that batch cross a controller boundary?</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>The principle was agreed on the 6 August call: it is handled with the same logic as a Z-mill coil break, with a supervisor judging the material already on the spool against the planned weight. If there is enough material, approach the customer for a concession — "will you still take this, it's underweight by 250 pounds". If the break is early in the run, reject the material, strip the spool, mount an empty one, replan onto another input rod and rerun the order. You flagged this yourself as a genuine one-off — a customer ordering one or two skids rather than a truckload, who also refuses welds — and cautioned against over-engineering it.</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>Same logic as a Z-mill coil break. The judgement is a supervisor's, made on the total footage or weight already on the spool against the planned weight. Enough material means approach the customer for a concession; early in the run means reject, strip the spool, mount an empty spool, replan onto another input rod and rerun.</t>
-        </is>
-      </c>
+          <r>
+            <t xml:space="preserve">Every published machine map addresses the finishing mill stands under FL2. FL3 is the hybrid route and needs both mills configured, sent as a single batch on one acknowledgement. So either the finishing mill is physically owned by the FL2 controller and FL3 reaches it through FL2's address space — in which case the FL3 send writes to </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>two controllers</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> in one logical batch — or FL3 has its own address space for it and the send is one controller.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H32" s="10" t="n"/>
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="10" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Reuse the Z-mill disposition set and the existing screens — warehouse, scrap, continue, hold — with concession handled through the existing coil-break e-mail flow, and persist the decision in the run-event history. </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Confirm the frequency before we size anything.</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> If it is genuinely a one-off, the right build is a supervisor disposition on existing rails and </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>no new screen</t>
-          </r>
-          <r>
-            <t>.</t>
+            <t xml:space="preserve">We will assume the finishing mill is owned by the FL2 controller and that FL3 reaches it through FL2's address space, and </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>design the FL3 send for two controllers from the start</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> — a per-controller batch with an explicit compensating clear on partial failure. Please confirm or correct.</t>
           </r>
         </is>
       </c>
       <c r="K32" s="10" t="inlineStr">
         <is>
-          <t>We are taking your own caution seriously: building a dedicated path for a case that may never recur is the wrong trade against a 30 September window.</t>
+          <t>That is the harder of the two cases, and building for it costs little now whereas discovering it at commissioning costs a redesign of the send. It also decides what a partial failure looks like and what the compensating clear has to undo — which is not a naming preference.</t>
         </is>
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>A no-weld customer's wire break has no defined disposition path, and the persistence target is undecided.</t>
-        </is>
-      </c>
-      <c r="M32" s="10" t="n"/>
+          <t>The hybrid send is designed against an assumption about controller ownership, and the existing commissioning test passes either way so it cannot detect a wrong guess.</t>
+        </is>
+      </c>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>Q27</t>
+        </is>
+      </c>
       <c r="N32" s="8" t="n"/>
       <c r="O32" s="8" t="n"/>
       <c r="P32" s="8" t="n"/>
@@ -5614,12 +5618,12 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Q32</t>
+          <t>Q30</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Machine interface</t>
+          <t>Weights and measurement</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -5629,7 +5633,7 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Tim O., Engineering</t>
+          <t>Tim O., Bob S., Engineering</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -5640,164 +5644,96 @@
       <c r="F33" s="7" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">⚠ </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>We may have this wrong, and we would rather say so than present a clean recommendation.</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> Five points on the FM2 dancer modes. Who selects the mode — the operator, the pass schedule, or is it fixed per product? Both dancers always in the same mode, or set independently? Is the mode a </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>pass schedule parameter</t>
-          </r>
-          <r>
-            <t xml:space="preserve">, in which case it is sent to the machine at check-in, or a </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>machine-side setting</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> the system only reads? If it is sent, what carries it? And in tension mode, is a tension setpoint entered, and where does it come from?</t>
+            <t xml:space="preserve">Are there load cells on the take-ups? And is the spool completion weight </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>read</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> from them or </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>derived</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> from the footage counter and the measured cross-section? If both exist, which is authoritative when they disagree?</t>
           </r>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>You disclosed this equipment behaviour on the 6 August call: FM2 will have two dancers, positioned where the edgers are, each with a regular dancer mode for compensating speed control and a tension mode similar to the current mills. Nothing in our design models it. Two further points follow. Tension mode contradicts a rule we hold — that tension is derived from speed and never entered manually — which needs qualifying by mode rather than deleting. And the third question decides whether this adds schedule data or only a read subscription.</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">The equipment is on record — one dancer on FM1, two on FM2, between the first and second stands and between the second and third. What is missing is the model rather than the equipment. We have authored a </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>read-only</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> view of the mode, which holds whichever way the third question is answered; the write side is absent.</t>
-          </r>
-        </is>
-      </c>
+          <r>
+            <t xml:space="preserve">Two of our documents disagree. One records an assumption that load cells are fitted on both payoff positions and on both take-ups; the other states the completion weight is derived from live footage and measured cross-section. And no take-up weight signal appears in the machine interface on any line. So the interface currently specifies a behaviour — the machine-stop prompt fires when take-up weight reaches target, and the recorded value is what appears on the </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>printed label</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> — that reads a value with no published source.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H33" s="7" t="n"/>
       <c r="I33" s="7" t="n"/>
       <c r="J33" s="7" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">⚠ </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Read this against your own earlier statement before acting on it.</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> On 23 July you told us dancers </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>remove</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> tension rather than apply it, that tension control is primarily </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>machine-driven</t>
-          </r>
-          <r>
-            <t xml:space="preserve">, and that configuration values are controlled through process settings. If that is right, </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>this recommendation is wrong and the read-only view we have already built is the whole answer.</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> Our recommendation, left standing deliberately so you can knock it down: model the mode as a </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>pass schedule parameter</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> rather than a machine-side setting we merely read, and set it </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>per dancer</t>
-          </r>
-          <r>
-            <t>, since the two sit in different positions. A second engineering question rides on the same answer: if dancers remove rather than apply tension, then our model of applied tension reducing roll separating force may be modelling something the equipment does not do — and that feeds through to the calculated roll gap.</t>
+            <t xml:space="preserve">Specify the completion weight as </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>derived from footage and cross-section</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, and treat any take-up load cell as a </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>corroborating</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> reading rather than the source. If the cells exist, tell us and we will add their signals so commissioning can read them — but the transaction will not depend on them.</t>
           </r>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>We recommend the schedule-parameter treatment because the mode changes two calculated values on the pass schedule — separating force, and therefore roll gap — so a read-only treatment would let the schedule and the machine disagree about the physics. But the 23 July statement argues the opposite and it is the earlier, more specific one. Both readings may even be true: a dancer can physically absorb tension while still offering a machine-side tension mode. This is an engineering answer, not an editorial one, which is why we are showing you the conflict rather than resolving it ourselves.</t>
+          <t>It puts the scale-versus-calculated reconciliation in one place, one level down, instead of creating two competing rules at this level. Note the consequence: if the weight is derived, its accuracy rests entirely on the footage-to-weight dimensional basis, which is separately open and already critical.</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <r>
-            <t xml:space="preserve">Until this closes we generate pass schedules untensioned and flagged — conservative for force, but </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>not</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> for gauge, so the calculated roll gap may deliver thin in tension mode.</t>
-          </r>
-        </is>
-      </c>
-      <c r="M33" s="7" t="n"/>
+          <t>The most consequential number in the completion transaction — the one printed on the label — has no confirmed source.</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
       <c r="N33" s="8" t="n"/>
       <c r="O33" s="8" t="n"/>
       <c r="P33" s="8" t="n"/>
@@ -5806,12 +5742,12 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Q33</t>
+          <t>Q31</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Weights and measurement</t>
+          <t>Rod checkout and partial material</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -5821,46 +5757,70 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Tim O.</t>
+          <t>Tim O., Shannon R.</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>Confirmation of our reading</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>When a spool is measured by its outer diameter at the take-up, how is the remaining weight calculated? We need the formula confirmed and documented.</t>
+          <t>Four points remain on the no-weld wire break. Is the disposition list exactly the Z-mill set — return to warehouse, scrap, continue processing, hold, concession — and does it reuse the existing screen? Is the supervisor gate a credential block, or an operator decision recorded against a supervisor's name? Does the concession path reuse the existing coil-break e-mail flow? And, before any of that, how often does this actually happen?</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Weight distribution is already tracked through footage and revolutions, but the diameter-based verification calculation is a separate thing and is still needed before spool weight tracking and as-is stock handling can be built.</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="n"/>
+          <t>The principle was agreed on the 6 August call: it is handled with the same logic as a Z-mill coil break, with a supervisor judging the material already on the spool against the planned weight. If there is enough material, approach the customer for a concession — "will you still take this, it's underweight by 250 pounds". If the break is early in the run, reject the material, strip the spool, mount an empty one, replan onto another input rod and rerun the order. You flagged this yourself as a genuine one-off — a customer ordering one or two skids rather than a truckload, who also refuses welds — and cautioned against over-engineering it.</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Same logic as a Z-mill coil break. The judgement is a supervisor's, made on the total footage or weight already on the spool against the planned weight. Enough material means approach the customer for a concession; early in the run means reject, strip the spool, mount an empty spool, replan onto another input rod and rerun.</t>
+        </is>
+      </c>
       <c r="I34" s="10" t="n"/>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>Derive it from the same single footage-to-weight factor rather than as an independent formula — the volume of the annulus from outer diameter, inner diameter and coil width, times alloy density — so spool weight, coil weight and the printed label all trace back to one number.</t>
+          <r>
+            <t xml:space="preserve">Reuse the Z-mill disposition set and the existing screens — warehouse, scrap, continue, hold — with concession handled through the existing coil-break e-mail flow, and persist the decision in the run-event history. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Confirm the frequency before we size anything.</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> If it is genuinely a one-off, the right build is a supervisor disposition on existing rails and </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>no new screen</t>
+          </r>
+          <r>
+            <t>.</t>
+          </r>
         </is>
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>Two independently confirmed formulas will disagree in the third decimal and nobody will know which is authoritative. The accumulated scale-versus-calculated variances are the data that would validate this one.</t>
+          <t>We are taking your own caution seriously: building a dedicated path for a case that may never recur is the wrong trade against a 30 September window.</t>
         </is>
       </c>
       <c r="L34" s="10" t="inlineStr">
         <is>
-          <t>Spool weight tracking and as-is stock handling cannot be implemented.</t>
-        </is>
-      </c>
-      <c r="M34" s="10" t="inlineStr">
-        <is>
-          <t>Q10</t>
-        </is>
-      </c>
+          <t>A no-weld customer's wire break has no defined disposition path, and the persistence target is undecided.</t>
+        </is>
+      </c>
+      <c r="M34" s="10" t="n"/>
       <c r="N34" s="8" t="n"/>
       <c r="O34" s="8" t="n"/>
       <c r="P34" s="8" t="n"/>
@@ -5869,22 +5829,22 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Q16</t>
+          <t>Q32</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Planning and scheduling</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Machine interface</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Tim O., Stephen</t>
+          <t>Tim O., Engineering</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -5894,29 +5854,162 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>Should planning or scheduling warn when a job is booked on a flattening line but no pass schedule exists for that product's alloy, gauge, width and edge type?</t>
+          <r>
+            <t xml:space="preserve">⚠ </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>We may have this wrong, and we would rather say so than present a clean recommendation.</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Five points on the FM2 dancer modes. Who selects the mode — the operator, the pass schedule, or is it fixed per product? Both dancers always in the same mode, or set independently? Is the mode a </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>pass schedule parameter</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, in which case it is sent to the machine at check-in, or a </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>machine-side setting</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> the system only reads? If it is sent, what carries it? And in tension mode, is a tension setpoint entered, and where does it come from?</t>
+          </r>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Without a check at scheduling time, operators arrive at the machine ready to run and find no schedule available, and the line waits while Operations authors one. The hard gate at check-in is being handled separately.</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="n"/>
+          <t>You disclosed this equipment behaviour on the 6 August call: FM2 will have two dancers, positioned where the edgers are, each with a regular dancer mode for compensating speed control and a tension mode similar to the current mills. Nothing in our design models it. Two further points follow. Tension mode contradicts a rule we hold — that tension is derived from speed and never entered manually — which needs qualifying by mode rather than deleting. And the third question decides whether this adds schedule data or only a read subscription.</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">The equipment is on record — one dancer on FM1, two on FM2, between the first and second stands and between the second and third. What is missing is the model rather than the equipment. We have authored a </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>read-only</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> view of the mode, which holds whichever way the third question is answered; the write side is absent.</t>
+          </r>
+        </is>
+      </c>
       <c r="I35" s="7" t="n"/>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>Warn at scheduling time, do not block. A scheduler should be able to book work before Operations has authored the schedule, but not unknowingly. Check-in provides the hard gate at the point it matters.</t>
+          <r>
+            <t xml:space="preserve">⚠ </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Read this against your own earlier statement before acting on it.</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> On 23 July you told us dancers </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>remove</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> tension rather than apply it, that tension control is primarily </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>machine-driven</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, and that configuration values are controlled through process settings. If that is right, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>this recommendation is wrong and the read-only view we have already built is the whole answer.</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Our recommendation, left standing deliberately so you can knock it down: model the mode as a </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>pass schedule parameter</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> rather than a machine-side setting we merely read, and set it </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>per dancer</t>
+          </r>
+          <r>
+            <t>, since the two sit in different positions. A second engineering question rides on the same answer: if dancers remove rather than apply tension, then our model of applied tension reducing roll separating force may be modelling something the equipment does not do — and that feeds through to the calculated roll gap.</t>
+          </r>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>Warning at scheduling plus blocking at check-in covers the failure without making planning depend on pass schedule authoring being finished first.</t>
+          <t>We recommend the schedule-parameter treatment because the mode changes two calculated values on the pass schedule — separating force, and therefore roll gap — so a read-only treatment would let the schedule and the machine disagree about the physics. But the 23 July statement argues the opposite and it is the earlier, more specific one. Both readings may even be true: a dancer can physically absorb tension while still offering a machine-side tension mode. This is an engineering answer, not an editorial one, which is why we are showing you the conflict rather than resolving it ourselves.</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>Lines will occasionally sit waiting for a schedule that could have been flagged days earlier.</t>
+          <r>
+            <t xml:space="preserve">Until this closes we generate pass schedules untensioned and flagged — conservative for force, but </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>not</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> for gauge, so the calculated roll gap may deliver thin in tension mode.</t>
+          </r>
         </is>
       </c>
       <c r="M35" s="7" t="n"/>
@@ -5928,17 +6021,17 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Q19</t>
+          <t>Q33</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Spool lifecycle</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Weights and measurement</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
@@ -5953,32 +6046,36 @@
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>The 75 / 90 / 100 per cent approaching-target notification was specified for spool creation at FL1. FL2 and FL3 wind finished coils at the second take-up with the same concern. Should the same notification run there with coil wording and the coil target weight?</t>
+          <t>When a spool is measured by its outer diameter at the take-up, how is the remaining weight calculated? We need the formula confirmed and documented.</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>The operator concern is identical at both places. One point to note if the answer is yes: FL2 running standalone does not broadcast live gauge and width, so its weight-per-foot factor has to come from the pass schedule or the order rather than from live measurement.</t>
+          <t>Weight distribution is already tracked through footage and revolutions, but the diameter-based verification calculation is a separate thing and is still needed before spool weight tracking and as-is stock handling can be built.</t>
         </is>
       </c>
       <c r="H36" s="10" t="n"/>
       <c r="I36" s="10" t="n"/>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>Yes — run the same 75 / 90 / 100 ladder at the finished-coil take-up, with coil wording and the coil target weight. On FL2 standalone the weight-per-foot factor comes from the pass schedule or order, and it is the same factor as elsewhere rather than a new one.</t>
+          <t>Derive it from the same single footage-to-weight factor rather than as an independent formula — the volume of the annulus from outer diameter, inner diameter and coil width, times alloy density — so spool weight, coil weight and the printed label all trace back to one number.</t>
         </is>
       </c>
       <c r="K36" s="10" t="inlineStr">
         <is>
-          <t>The operator concern is identical, and a second differently-shaped notification on the same shop floor is a training cost for no benefit.</t>
+          <t>Two independently confirmed formulas will disagree in the third decimal and nobody will know which is authoritative. The accumulated scale-versus-calculated variances are the data that would validate this one.</t>
         </is>
       </c>
       <c r="L36" s="10" t="inlineStr">
         <is>
-          <t>Finished-coil completion has no approaching-target warning, so operators get no notice before the coil reaches weight.</t>
-        </is>
-      </c>
-      <c r="M36" s="10" t="n"/>
+          <t>Spool weight tracking and as-is stock handling cannot be implemented.</t>
+        </is>
+      </c>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
       <c r="N36" s="8" t="n"/>
       <c r="O36" s="8" t="n"/>
       <c r="P36" s="8" t="n"/>
@@ -5987,79 +6084,1624 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Q20</t>
+          <t>Q34</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Spool lifecycle</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Shared plant records</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Tim O., IT</t>
+          <t>Tim O. / IT</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Confirmation of our reading</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <r>
-            <t xml:space="preserve">Is the spool completion alert operator-only, or is it also shown to the supervisor — particularly an </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>unacknowledged</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> 100 per cent milestone, which means nobody is at the machine while the spool fills? And where is the acknowledgement recorded for audit?</t>
-          </r>
+          <t>Completing a flat wire coil now creates the same set of plant records any other finished coil has, and each of those records carries a short transaction name. What name should a flat wire coil completion use, and does any existing report, screen or process filter on that name in a way a new value would disturb?</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>An unanswered completion notification is a specific and actionable signal: the spool is filling and no one is responding. The other two rungs of the ladder are not, and mirroring all three would teach a supervisor to ignore the notification.</t>
+          <t>Three of the records created at coil completion carry a transaction name, and all three use the same eight-character field. Reusing an existing name would make a flat wire completion indistinguishable from the skid creation the slitters do, which defeats the purpose of recording it. One other existing name would additionally cause a duplicate history entry to be written.</t>
         </is>
       </c>
       <c r="H37" s="7" t="n"/>
       <c r="I37" s="7" t="n"/>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>Mirror only the unacknowledged 100 per cent milestone to the supervisor, not the whole ladder. Record the acknowledgement in the existing run-event history rather than a new record type.</t>
+          <t>A new name reserved for flat wire, eight characters so it fits the field exactly, used consistently across all three records so that one completion is traceable end to end.</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>The unanswered completion is the one state a supervisor needs; mirroring everything trains them to ignore it. An acknowledgement is an event with an actor and a timestamp, which is exactly what the run-event history already holds.</t>
+          <t>This is the one value in the new records that every existing consumer of the shop-floor history can see, and we cannot tell from the code which reports depend on that column — the impact review that would have told us was removed along with the shared-schema changes. It is a short conversation and an expensive thing to get wrong, because a wrong value does not raise an error: it writes a name an existing report may quietly filter out.</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>Supervisors get no visibility of an unattended machine at spool completion, and the acknowledgement has no confirmed audit home.</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="n"/>
+          <t>The work can be built and tested against development copies, but must not run against live plant data.</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>Q35</t>
+        </is>
+      </c>
       <c r="N37" s="8" t="n"/>
       <c r="O37" s="8" t="n"/>
       <c r="P37" s="8" t="n"/>
       <c r="Q37" s="8" t="n"/>
     </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Q35</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Shared plant records</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>Tim O. / IT</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>Confirmation of our reading</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>The finished coil record created at completion needs a status value. Should a finished flat wire coil carry the existing status used for a coil that is complete and on a skid, or does finished flat wire need to be distinguishable from other finished material by its status?</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>The existing status is accurate — the coil is complete and it is on a skid — and it is exactly what the equivalent transaction writes for a slitter coil. A new value would be an addition to a status vocabulary that every system in the plant reads.</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>Reuse the existing status. Introduce a new value only if a named report or process actually requires flat wire to be told apart, in which case the right change is to that report rather than to the shared vocabulary.</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>The question is not what the coil is, which is settled, but whether anything downstream needs to distinguish it. If something does, we would rather find out now than after the first coil is written, because a status value is read far more widely than it is written.</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>As Q34 — buildable, but not against live plant data.</t>
+        </is>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>Q34</t>
+        </is>
+      </c>
+      <c r="N38" s="8" t="n"/>
+      <c r="O38" s="8" t="n"/>
+      <c r="P38" s="8" t="n"/>
+      <c r="Q38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Q37</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Shared plant records</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Tim O. / IT</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Confirmation of our reading</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Checking a rod in at a flattening line now creates a set of records in the existing plant systems, several of which carry a short transaction name. What name should a flat wire rod check-in use, and does any existing report, screen or process filter on that name in a way a new value would disturb?</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Nine plant records are written when a rod is checked in, and several of them carry the same eight-character transaction name field every other operation uses. Reusing an existing operation's name would make a flat wire check-in indistinguishable from that operation in the shop-floor history, which defeats the point of recording it at all.</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="n"/>
+      <c r="I39" s="7" t="n"/>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>A new name reserved for flat wire check-in, eight characters so it fits the field exactly, used consistently across every record written by the same check-in so one transaction is traceable from end to end.</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>This is the most widely visible of the new values — every existing consumer of the shop-floor history can see it — and we cannot tell from the code which reports depend on it, because the impact review that would have told us was removed along with the shared-schema changes. A wrong value does not raise an error: it writes a name an existing report may quietly filter out.</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>The work can be built and tested against development copies, but must not run against live plant data.</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>Q38, Q39, Q40</t>
+        </is>
+      </c>
+      <c r="N39" s="8" t="n"/>
+      <c r="O39" s="8" t="n"/>
+      <c r="P39" s="8" t="n"/>
+      <c r="Q39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Q38</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Shared plant records</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Tim O. / IT</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>Confirmation of our reading</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>The shop-floor history entry written when a rod is checked in needs a status value describing what is happening to the material. Does flat wire need a status of its own here, or should it reuse the value already used for material on a rolling mill?</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>A new status value would be an addition to a vocabulary every system in the plant reads, and adding to shared vocabularies is exactly the class of change that was cancelled when the shared-schema work was dropped. The existing rolling value is accurate — the material is on a mill being rolled. The flat wire module does keep a flattening status of its own internally, which nothing outside it sees.</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="10" t="n"/>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>Reuse the existing rolling status. Introduce a flat-wire-specific value only if a named report or process genuinely needs to tell flattening from rolling in the history, in which case the right change is to that report rather than to the shared vocabulary.</t>
+        </is>
+      </c>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>A status value is read far more widely than it is written, so the cost of a new one is spread across systems nobody is currently looking at. If something does need the distinction we would rather find out now than after the first rod runs.</t>
+        </is>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>As Q37 — buildable, but not against live plant data.</t>
+        </is>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>Q37</t>
+        </is>
+      </c>
+      <c r="N40" s="8" t="n"/>
+      <c r="O40" s="8" t="n"/>
+      <c r="P40" s="8" t="n"/>
+      <c r="Q40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Q39</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Shared plant records</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Tim O. / IT</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Confirmation of our reading</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>When a rod is checked in we propose stamping its existing material record with the station it is being processed at, the operator badge, the transaction name and the time — the same marks every other operation leaves. Is that safe for the reports and screens that already read those fields?</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">With the shared-schema changes cancelled, nothing outside the flat wire module now marks a rod as being on a flattening line, so a rod can be in process with no sign of it anywhere else. Stamping these four fields restores that visibility using columns that already exist. We are deliberately </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>not</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> changing the material's status, which is the field read most widely of all.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H41" s="7" t="n"/>
+      <c r="I41" s="7" t="n"/>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>Write all four. They are how every operation marks material as being worked, the values are ordinary ones, and leaving them blank is what created the visibility gap in the first place.</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>The alternative is a rod being processed with nothing in the plant record to say where it is, which was judged unacceptable when we found it. We are asking you to confirm rather than assume, because this is the one place flat wire becomes visible in the wider system at all.</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>As Q37 — buildable, but not against live plant data, and the visibility gap stays open until it runs.</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>Q37</t>
+        </is>
+      </c>
+      <c r="N41" s="8" t="n"/>
+      <c r="O41" s="8" t="n"/>
+      <c r="P41" s="8" t="n"/>
+      <c r="Q41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Q40</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Shared plant records</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Tim O. / IT</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>Checking a rod in writes a requirement record against the order, showing the material the order has claimed. If the rod is then taken back off the line before anything has been made, that record has to be reversed. Should the reversal remove the record entirely, or leave it in place with its quantities set to zero?</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>The reversal already refuses to run once any material has been produced, because at that point the order genuinely did receive material. So this question is only about the case where the rod comes off having made nothing.</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>(1) Delete the record, leaving no trace of the claim. (2) Leave the record and set its quantities to zero.</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>Leave it and zero it. A deleted record destroys the evidence that the material was ever claimed against the order; a zeroed one is auditable and can be corrected. Please tell us if any existing report counts these records rather than summing their quantities — that is the one case where a zeroed record reads differently from an absent one.</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>Both directions are recoverable except one: you can always zero a record you decided to keep, and you cannot restore one you decided to delete. Where the two are otherwise equal we would rather keep the audit trail.</t>
+        </is>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>We will build the safer direction — zeroing — so that a missing answer never causes a deletion.</t>
+        </is>
+      </c>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>Q37</t>
+        </is>
+      </c>
+      <c r="N42" s="8" t="n"/>
+      <c r="O42" s="8" t="n"/>
+      <c r="P42" s="8" t="n"/>
+      <c r="Q42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Q42</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Spool lifecycle</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Tim O. / Bob S.</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Values or data</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>What will the numbers stencilled on the spools look like, and how many spools will there be in the end? The screens accept the number as typed and check it against a registered list, so we need that list.</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>You have confirmed the spools are reusable physical carriers identified much like furnace plates — thirty purchased, with a decision on a further fifteen pending, and all of one standard size. The number is typed and checked rather than chosen from a list, because thirty to forty-five entries is too long to scroll on a shop-floor panel.</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>Spool numbers are static and stencilled on the spool, not generated per job. All spools are one standard size. The number is entered as text and validated, not selected from a drop-down.</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="n"/>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>Whatever nomenclature you decide to stencil, given to us as a plain list so we can load it. We will accept the number as typed and ignore capitalisation, since the operator is reading paint off steel. We hold the list inside the flat wire module rather than adding it to an existing plant table, so adding or retiring a spool is a data change and nothing more.</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>Until the list exists the number cannot be checked, and an unchecked number is worse than no number: a mistyped entry would be accepted and the material would be recorded against the wrong carrier, which then travels through the furnace and arrives at FL2 mislabelled.</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>We will build the validation against a placeholder list and swap it, but nothing can be tested end to end until the real numbers exist.</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>Q44</t>
+        </is>
+      </c>
+      <c r="N43" s="8" t="n"/>
+      <c r="O43" s="8" t="n"/>
+      <c r="P43" s="8" t="n"/>
+      <c r="Q43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Q43</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Spool lifecycle</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Tim O. / Planning</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>A spool can carry more than one order. When it is checked in at FL2, does the operator choose which order is being made, or should the system determine it? And is there a practical limit to how many orders one spool can carry?</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>You confirmed that a spool coming off FL1 may carry two or more orders, while FL2 makes one order at a time. Separately, a spool with no order at all is a legitimate case — a planning remainder, or a part-run spool accepted back by a supervisor — and the spool queue screen already allows such a spool to be checked in.</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>A spool may carry several source rods and several orders. FL2 makes one order at a time out of a spool.</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>(1) The operator selects the order at check-in from those on the spool. (2) The system derives it from the material expected off the spool first. (3) Planning nominates the order and the operator cannot change it.</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>Option 1, defaulted from option 2 — planning allocates the set of orders to the spool, the system offers the order of the material expected off first, and the operator can change it. That makes the common case a single keypress and still lets the operator correct it when the spool is threaded the other way round. We would not put a limit in the system on how many orders a spool may carry; the check that matters is that the order chosen is genuinely one of those on the spool.</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>Deciding this now rather than later is what stops the records being designed around a single order and rebuilt when the second one appears. It also settles whether a spool with no order can still be run, which the screens currently allow and the underlying records currently forbid — a contradiction we would rather resolve deliberately than discover on a shift.</t>
+        </is>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>Order allocation on a spool cannot be recorded, and the one documented case of a spool with no order cannot be checked in at all.</t>
+        </is>
+      </c>
+      <c r="M44" s="10" t="n"/>
+      <c r="N44" s="8" t="n"/>
+      <c r="O44" s="8" t="n"/>
+      <c r="P44" s="8" t="n"/>
+      <c r="Q44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Q44</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Spool lifecycle</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Tim O. / Bob S.</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Exactly what should print on the spool label, and will the etched steel plates you are investigating replace the label or sit alongside it?</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>The label itself is settled: the inch-and-a-half by three-inch high-temperature label already used on mill output, two to a label so one goes on each side of the spool, printed when the spool is completed, carrying the spool number and the material identities on it. Nothing else survives the anneal. What is not settled is the full list of what prints, and this document has referred to printing the labels throughout without ever stating it.</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>The high-temperature label, two per spool, one per side. It carries the spool number and the material identities on the spool, and scanning any one of them at FL2 finds the spool — the same way scanning one identity on a furnace plate gets the plate into anneal.</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="n"/>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>Print the spool number, every material identity on the spool with the weight each contributed, and the order or orders. The spool number is the primary barcode and each material identity a secondary, so the operator can scan whichever is facing them. The pass schedule stays off the label, as agreed previously. If the etched plates prove workable, we would suggest they carry the spool number only and sit alongside the label rather than replacing it — the spool is permanent and so is the etching, whereas the material on it changes every cycle.</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>The weights are the part worth deciding deliberately: they are what the welding wire certificates are built from, and they depend on the footage-to-weight conversion still outstanding. Printing a number derived from an unconfirmed conversion is worse than not printing it, because a figure on a label is treated as measured.</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>The label prints the spool number and the identities only, and any weight has to be looked up on a screen instead.</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>Q42</t>
+        </is>
+      </c>
+      <c r="N45" s="8" t="n"/>
+      <c r="O45" s="8" t="n"/>
+      <c r="P45" s="8" t="n"/>
+      <c r="Q45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Q45</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Spool lifecycle</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Tim O. / Engineering</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>Confirmation of our reading</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>Does a spool always unwind in the reverse of the order it was wound, so that the last material on is the first off? And should the system therefore treat the identity leading the label as the one it requires at the next check-in, or as an expectation it must be willing to be wrong about?</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>You told us the spool runs in reverse, and that the identity leading the label should be the one expected at the next operation. It was also pointed out that FL1 runs continuously, so the finished coils cut from a spool cannot be sequenced in advance. Both statements are correct and they are about different things — the first about the source material going onto the spool, the second about the coils coming off it — but they lead to different behaviour at check-in, which is why we are asking.</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>The identity leading the printed label should be the one expected at the next check-in.</t>
+        </is>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>(1) The leading identity is required — scanning any other identity on the spool is refused. (2) It is expected — any identity on the spool is accepted, and the expected one is shown for information. (3) It is expected, and a mismatch warns without blocking.</t>
+        </is>
+      </c>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>Option 2. Show the expected identity prominently and accept any identity on the spool without a warning; the operator is holding the spool and the system is not. If engineering can confirm the unwind direction is genuinely guaranteed, please tell us — it would let the system catch a mis-threaded spool, which is a check we have no other way of making.</t>
+        </is>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>The two possible mistakes cost very different amounts. Treating an expectation as a rule stops a correct spool at check-in and puts the operator on the phone to a supervisor. Treating a rule as an expectation only loses a check nobody has today. Until the direction is confirmed, the permissive reading is the safe one.</t>
+        </is>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>We build the permissive behaviour, which is safe but leaves a mis-threaded spool undetected.</t>
+        </is>
+      </c>
+      <c r="M46" s="10" t="n"/>
+      <c r="N46" s="8" t="n"/>
+      <c r="O46" s="8" t="n"/>
+      <c r="P46" s="8" t="n"/>
+      <c r="Q46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Q49</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Planning and scheduling</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Tim O.</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Confirmation of our reading</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>The rule that a rod shared between orders is run last in its order applies when that rod is welded to the next one. Does it still apply when there is no weld?</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>The reason given for running a shared rod last was to keep the weld at the end of the order rather than in the middle of it. Where no weld is involved that reason does not apply, so it is unclear whether the sequencing rule is still wanted.</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="n"/>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>(1) The rule applies to every shared rod. (2) It applies only to welded ones.</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>Option 1 - apply it to every shared rod.</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>A single rule the operator can predict is worth more than a narrower one that is technically minimal, and the cost of running a shared rod last when it did not strictly need to be is nil.</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>The sequence check refuses rods presented out of order. If the rule is narrower than we have built, it will refuse work the plant considers perfectly normal.</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="n"/>
+      <c r="N47" s="8" t="n"/>
+      <c r="O47" s="8" t="n"/>
+      <c r="P47" s="8" t="n"/>
+      <c r="Q47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>Q50</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Weights and measurement</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Tim O. / Shannon R.</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>Values or data</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>Material keeps being produced between the moment an order's allocated weight is reached and the moment the operator confirms it. How much overrun is acceptable before someone is told, and who is told?</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>The line is deliberately not stopped when the allocation is reached, so some overrun is unavoidable. In the worked examples the overrun on one order equals the shortfall on the next to the pound, so it is not waste - but it is unattributed until someone decides where it belongs.</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>(1) A fixed number of pounds. (2) A percentage of the allocation. (3) A percentage with a pounds floor for small orders.</t>
+        </is>
+      </c>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>Option 3, starting at 2% with a 25 lb floor, adjustable without a code change.</t>
+        </is>
+      </c>
+      <c r="K48" s="10" t="inlineStr">
+        <is>
+          <t>A flat percentage is unusable on a small order, where 2% may be a few pounds and would fire constantly; a flat pounds figure is meaningless on a 40,000 lb run. Making it configurable lets the first month of real running set it rather than this meeting.</t>
+        </is>
+      </c>
+      <c r="L48" s="10" t="inlineStr">
+        <is>
+          <t>We have built a warning and a supervisor escalation, but the threshold is a guess. Set too low it will cry wolf on every order; set too high it will never fire.</t>
+        </is>
+      </c>
+      <c r="M48" s="10" t="n"/>
+      <c r="N48" s="8" t="n"/>
+      <c r="O48" s="8" t="n"/>
+      <c r="P48" s="8" t="n"/>
+      <c r="Q48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Q52</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Planning and scheduling</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Tim O. / Planning</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>If a rod shared between two orders runs out before the first order has had its allocated weight, does the plant bring another rod in to top that order up, or does the order ship short?</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>The planned split assumes the rod yields its nominal weight. Real rods vary, and the rod weight itself is one of three figures currently in circulation, so a shortfall is likely rather than exceptional.</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="n"/>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>(1) Top up from another rod, with supervisor authorisation. (2) Ship short and let planning decide. (3) Top up only above a stated shortfall.</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>Option 1.</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>An unplanned substitution already needs a supervisor, so the mechanism exists; and shipping short without asking is the outcome least likely to be what the customer wanted.</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>This decides whether bringing in an unplanned rod is a normal path needing a supervisor authorisation, which we have built, or an exception that should not arise.</t>
+        </is>
+      </c>
+      <c r="M49" s="7" t="n"/>
+      <c r="N49" s="8" t="n"/>
+      <c r="O49" s="8" t="n"/>
+      <c r="P49" s="8" t="n"/>
+      <c r="Q49" s="8" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>Q53</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>Certification and traceability</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>Tim O. / Shannon R.</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>Is an order counted as fulfilled by the pounds of rod consumed against it, or by the pounds of finished wire produced from it - and which of the two does the customer certificate quote?</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>The two figures differ by process loss, so they are never equal. Consumption is what the plant controls and can measure at the payoff; production is what the customer receives.</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>(1) Consumed pounds throughout. (2) Produced pounds throughout. (3) Track both; fulfil on consumed, certify on produced.</t>
+        </is>
+      </c>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>Option 3.</t>
+        </is>
+      </c>
+      <c r="K50" s="10" t="inlineStr">
+        <is>
+          <t>They answer different questions and both are wanted: the plant needs consumption to know when a rod's allocation is spent, and the customer needs produced weight because that is what arrives. Tracking both costs one extra stored figure and removes the need to choose.</t>
+        </is>
+      </c>
+      <c r="L50" s="10" t="inlineStr">
+        <is>
+          <t>Every fulfilment figure, the completion notification and the certificate all read from the same basis. Choosing later means changing all three together.</t>
+        </is>
+      </c>
+      <c r="M50" s="10" t="n"/>
+      <c r="N50" s="8" t="n"/>
+      <c r="O50" s="8" t="n"/>
+      <c r="P50" s="8" t="n"/>
+      <c r="Q50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Q54</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Spool lifecycle</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Tim O. / Bob S.</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>When the operator marks an order complete part-way through winding an FL1 spool, does that also close the spool, or may one spool carry material belonging to two orders?</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>A finished coil belongs to exactly one order. If a spool spans an order boundary, the finishing mill must cut at that boundary, and the worked examples show that turning a good 1,800 lb spool into two coils below the customer minimum. Closing the spool at the acknowledgement avoids that outright, at the cost of a lighter spool.</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="n"/>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>(1) The acknowledgement closes the spool. (2) A spool may span the boundary and the mill cuts at it. (3) It spans only if the material left exceeds one coil weight.</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>Option 1.</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>It removes the failure rather than managing it. A lighter spool costs a little anneal capacity; two sub-minimum coils cost the material and the order.</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>This is the strongest available fix for a known failure that otherwise makes unsellable coils from good material. Building it later means changing spool completion, the spool queue and the mill's cutting rules together.</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="n"/>
+      <c r="N51" s="8" t="n"/>
+      <c r="O51" s="8" t="n"/>
+      <c r="P51" s="8" t="n"/>
+      <c r="Q51" s="8" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Q87</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>Output and packaging</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>Tim O. / Bob S. / Shannon R.</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>What is printed on the label of the finished coil the customer receives, on what media - and where a coil was wound from two source rods, does the label carry one identifier or both?</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>The label the plant uses today prints as a sheet, so a single coil would waste most of one. The skid label is a candidate carrier instead, and something has to sit under the stretch wrap. Traceability wants both source identifiers recorded, but that is not the same as printing both on the face the customer sees.</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>Whatever is chosen must be consistent with the coil labels the plant already produces, and full traceability must be recorded even where it is not all printed on the customer-facing label.</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>(1) A coil label on new media. (2) Traceability on the skid label with a minimal coil label. (3) One identifier on the printed face, both recorded against the coil.</t>
+        </is>
+      </c>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>Option 3 for the identifiers, with the media decided together with Q4.</t>
+        </is>
+      </c>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
+          <t>A customer reading two identifiers on one coil has to work out what that means; the certificate is the right place for the full genealogy, and the coil record already holds it. The media half genuinely depends on the skid decision and should not be settled separately.</t>
+        </is>
+      </c>
+      <c r="L52" s="10" t="inlineStr">
+        <is>
+          <t>Deferred on the 24 August call. Coil completion cannot be finished without it, and it is bound up with the skid labelling question - the same decision seen from the other end.</t>
+        </is>
+      </c>
+      <c r="M52" s="10" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="N52" s="8" t="n"/>
+      <c r="O52" s="8" t="n"/>
+      <c r="P52" s="8" t="n"/>
+      <c r="Q52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Q16</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Planning and scheduling</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Tim O., Stephen</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Should planning or scheduling warn when a job is booked on a flattening line but no pass schedule exists for that product's alloy, gauge, width and edge type?</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Without a check at scheduling time, operators arrive at the machine ready to run and find no schedule available, and the line waits while Operations authors one. The hard gate at check-in is being handled separately.</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="n"/>
+      <c r="I53" s="7" t="n"/>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>Warn at scheduling time, do not block. A scheduler should be able to book work before Operations has authored the schedule, but not unknowingly. Check-in provides the hard gate at the point it matters.</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>Warning at scheduling plus blocking at check-in covers the failure without making planning depend on pass schedule authoring being finished first.</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>Lines will occasionally sit waiting for a schedule that could have been flagged days earlier.</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="n"/>
+      <c r="N53" s="8" t="n"/>
+      <c r="O53" s="8" t="n"/>
+      <c r="P53" s="8" t="n"/>
+      <c r="Q53" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Q19</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Spool lifecycle</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>Tim O.</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>Confirmation of our reading</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>The 75 / 90 / 100 per cent approaching-target notification was specified for spool creation at FL1. FL2 and FL3 wind finished coils at the second take-up with the same concern. Should the same notification run there with coil wording and the coil target weight?</t>
+        </is>
+      </c>
+      <c r="G54" s="10" t="inlineStr">
+        <is>
+          <t>The operator concern is identical at both places. One point to note if the answer is yes: FL2 running standalone does not broadcast live gauge and width, so its weight-per-foot factor has to come from the pass schedule or the order rather than from live measurement.</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="10" t="n"/>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>Yes — run the same 75 / 90 / 100 ladder at the finished-coil take-up, with coil wording and the coil target weight. On FL2 standalone the weight-per-foot factor comes from the pass schedule or order, and it is the same factor as elsewhere rather than a new one.</t>
+        </is>
+      </c>
+      <c r="K54" s="10" t="inlineStr">
+        <is>
+          <t>The operator concern is identical, and a second differently-shaped notification on the same shop floor is a training cost for no benefit.</t>
+        </is>
+      </c>
+      <c r="L54" s="10" t="inlineStr">
+        <is>
+          <t>Finished-coil completion has no approaching-target warning, so operators get no notice before the coil reaches weight.</t>
+        </is>
+      </c>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="8" t="n"/>
+      <c r="O54" s="8" t="n"/>
+      <c r="P54" s="8" t="n"/>
+      <c r="Q54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Q20</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Spool lifecycle</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Tim O., IT</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Is the spool completion alert operator-only, or is it also shown to the supervisor — particularly an </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>unacknowledged</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> 100 per cent milestone, which means nobody is at the machine while the spool fills? And where is the acknowledgement recorded for audit?</t>
+          </r>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>An unanswered completion notification is a specific and actionable signal: the spool is filling and no one is responding. The other two rungs of the ladder are not, and mirroring all three would teach a supervisor to ignore the notification.</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="n"/>
+      <c r="I55" s="7" t="n"/>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>Mirror only the unacknowledged 100 per cent milestone to the supervisor, not the whole ladder. Record the acknowledgement in the existing run-event history rather than a new record type.</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>The unanswered completion is the one state a supervisor needs; mirroring everything trains them to ignore it. An acknowledgement is an event with an actor and a timestamp, which is exactly what the run-event history already holds.</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>Supervisors get no visibility of an unattended machine at spool completion, and the acknowledgement has no confirmed audit home.</t>
+        </is>
+      </c>
+      <c r="M55" s="7" t="n"/>
+      <c r="N55" s="8" t="n"/>
+      <c r="O55" s="8" t="n"/>
+      <c r="P55" s="8" t="n"/>
+      <c r="Q55" s="8" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Q36</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>Shared plant records</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>Tim O. / Planning</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>Confirmation of our reading</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>The record linking a finished coil to its order carries a sample number and a planned-operations value. Where the source rod already has an order record these are copied from it. Where it does not, what should a flat wire output coil carry?</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>Copying from the rod is established behaviour and needs no decision. The fallback only applies when a rod reaches coil completion without an order record, which should not happen if check-in worked correctly — so this is a question about what a defensive path should write.</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="n"/>
+      <c r="I56" s="10" t="n"/>
+      <c r="J56" s="10" t="inlineStr">
+        <is>
+          <t>Copy from the rod wherever a record exists, and fall back to the same values the equivalent slitter transaction uses. Only the fallback needs confirming.</t>
+        </is>
+      </c>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
+          <t>The cost of being wrong is a misleading sample number on an edge case rather than a broken transaction, which is why we have ranked this below the other two. But a defensive path that writes a plausible wrong value is harder to notice later than one that writes nothing.</t>
+        </is>
+      </c>
+      <c r="L56" s="10" t="inlineStr">
+        <is>
+          <t>Minor. A rod arriving at completion without an order record would be linked with an unconfirmed sample number.</t>
+        </is>
+      </c>
+      <c r="M56" s="10" t="n"/>
+      <c r="N56" s="8" t="n"/>
+      <c r="O56" s="8" t="n"/>
+      <c r="P56" s="8" t="n"/>
+      <c r="Q56" s="8" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Q46</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Run start and machine setup</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Tim O.</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>Confirmation of our reading</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>You mentioned that the system needs to know the diameter of the mandrel fitted, comparing it to selecting the mandrel size on a slitter. Does this vary from spool to spool, or is it fixed by the one standard spool size?</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Nothing records this today. On a slitter the mandrel genuinely varies, which is why the operator selects it. Here you have also confirmed that every spool is the same standard size, which would make the diameter a fixed property rather than a choice.</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="n"/>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>(1) The operator selects it per spool when the spool is completed. (2) It is fixed by the standard spool size and recorded once, with no operator entry. (3) It is read from the machine.</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>Option 2, if the spools really are all one size. A box that can only ever hold one value is a box that will eventually be filled in wrongly, and the diameter belongs to the spool specification rather than to the shift. If it does vary, then option 1 — and it belongs on the spool completion step beside the spool number, not at check-in, which is at the other end of the machine.</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>It also feeds the outside-diameter to weight calculation. Taking the diameter from a permitted range rather than a single known value is how a calculated weight quietly drifts, and that weight ends up on a label and a certificate.</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>We record the diameter against the spool specification and do not ask the operator for it, which is reversible if you tell us it varies.</t>
+        </is>
+      </c>
+      <c r="M57" s="7" t="n"/>
+      <c r="N57" s="8" t="n"/>
+      <c r="O57" s="8" t="n"/>
+      <c r="P57" s="8" t="n"/>
+      <c r="Q57" s="8" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Q47</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>Planning and scheduling</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>Tim O. / Planning</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>Confirmation of our reading</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>When planning divides an order into finished coils, should it always divide by the customer's maximum coil weight, or should it try smaller weights downward from the maximum to find the one that leaves the least unusable material?</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>The method agreed is to take the planned weight, divide by the maximum finished coil weight, round down to a whole number of coils and multiply back — which stays inside the customer's tolerance and leaves no overage. On a 44,000 lb planned weight against a 900 lb maximum that gives 48 coils and 43,200 lb. The remaining question is narrower than the method: whether the maximum is simply the divisor, or the starting point of a search.</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>Plan to the maximum finished coil weight and work backwards. Maximise the spool weight coming off FL1 to make best use of anneal capacity, then respect the customer's minimum and maximum at FL2 so that no unshippable remainder is created — a coil below the customer minimum is scrap, not a short coil. Where the order quantity is smaller than one spool, the order quantity governs. The calculation runs on the planner's planned weight rather than the order weight, with the existing over-order warning.</t>
+        </is>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>(1) Always divide by the maximum. (2) Search downward from the maximum for the weight that minimises leftover material. (3) Search downward for the weight that minimises over-shipment against the order.</t>
+        </is>
+      </c>
+      <c r="J58" s="10" t="inlineStr">
+        <is>
+          <t>Option 1. Rounding down already guarantees no overage, and the largest coils mean the fewest cuts for us and the fewest units for the customer, which is the reason you gave for starting at the maximum. Show the planner what is left over and let them place it, rather than having the system choose a slightly different coil weight on every order for reasons the planner cannot see.</t>
+        </is>
+      </c>
+      <c r="K58" s="10" t="inlineStr">
+        <is>
+          <t>Both of you said to optimise to the maximum, but the question actually asked was about searching downward from it, and those are compatible statements that do not settle it. A search is easy to build and hard to predict at the planning desk, which is the wrong trade for a number a planner has to defend to a customer.</t>
+        </is>
+      </c>
+      <c r="L58" s="10" t="inlineStr">
+        <is>
+          <t>Planning is built to divide by the maximum. Changing it later is a calculation change rather than a redesign, so this is the least costly of the open planning questions to defer.</t>
+        </is>
+      </c>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="8" t="n"/>
+      <c r="O58" s="8" t="n"/>
+      <c r="P58" s="8" t="n"/>
+      <c r="Q58" s="8" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Q51</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Planning and scheduling</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Tim O. / Planning</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>An operator may mark an order complete before its allocated weight is reached, because they can see the material is finished. What happens to the pounds that were allocated and never run?</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>The system records the shortfall, so the number is not lost. What is undecided is whether those pounds return to the order to be made up later, move to the next order on the rod, or are written off as a short shipment.</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="n"/>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>(1) The order closes short and the remainder is written off. (2) The remainder returns to the order for a later rod. (3) The remainder moves to the next order on the rod.</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>Option 1, with the shortfall reported.</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>The operator acknowledged early because the material was genuinely done, which is a statement that the order is finished, not that it is owed more. Options 2 and 3 both re-plan on the operator's behalf from a single button press.</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>The order's material status is worked out from what was consumed. Without this rule an early acknowledgement leaves an order looking permanently part-filled, and planning cannot tell whether to schedule more material.</t>
+        </is>
+      </c>
+      <c r="M59" s="7" t="n"/>
+      <c r="N59" s="8" t="n"/>
+      <c r="O59" s="8" t="n"/>
+      <c r="P59" s="8" t="n"/>
+      <c r="Q59" s="8" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>Q59</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>Shared plant records</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>Tim O. / IT</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>Confirmation of our reading</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>Flat wire takes its identifiers from the same shared generator the rest of the plant uses. Can any other caller be handed an identifier that a flat wire spool segment is already using?</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>The generator works out the next free number by scanning the tables it knows about. The flat wire database is not among them, so prior flat wire identifiers are passed in explicitly on every call. That works only for as long as every caller does it.</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>(1) Confirm no other caller can collide. (2) Add flat wire to the generator's own scan. (3) Reserve a number range for flat wire.</t>
+        </is>
+      </c>
+      <c r="J60" s="10" t="inlineStr">
+        <is>
+          <t>Option 3 if a range is available, otherwise option 2.</t>
+        </is>
+      </c>
+      <c r="K60" s="10" t="inlineStr">
+        <is>
+          <t>Both remove the dependency on every future caller remembering to pass prior identifiers in. A reserved range is the simpler of the two and needs no change to a shared piece of plumbing that four databases already depend on.</t>
+        </is>
+      </c>
+      <c r="L60" s="10" t="inlineStr">
+        <is>
+          <t>A duplicated identifier across two modules is the kind of defect found at certification rather than at build, and it cannot be put right once labels are printed.</t>
+        </is>
+      </c>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="8" t="n"/>
+      <c r="O60" s="8" t="n"/>
+      <c r="P60" s="8" t="n"/>
+      <c r="Q60" s="8" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Q55</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Spool lifecycle</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Tim O. / Bob S.</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Confirmation of our reading</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>The reusable stencilled spool and the batch of material wound onto it are two different things, and both get a number. Should they be told apart by their prefix, or is the context always enough?</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>The physical spool is stencilled once and used for years; the material on it changes every run. Today both read as SP- numbers of different lengths.</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="n"/>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>(1) Keep one prefix and rely on context. (2) Give the carrier its own prefix.</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>Option 2, with SC- for the carrier.</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>Two things sharing a prefix and differing only in how many digits follow is the kind of distinction that survives in a specification and not on a shop floor at shift change. This is the cheapest moment it will ever be to separate them.</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>A cosmetic choice with a long tail: the prefix is stencilled onto physical equipment and appears on labels, so changing it after the first batch is stencilled is not a software change.</t>
+        </is>
+      </c>
+      <c r="M61" s="7" t="n"/>
+      <c r="N61" s="8" t="n"/>
+      <c r="O61" s="8" t="n"/>
+      <c r="P61" s="8" t="n"/>
+      <c r="Q61" s="8" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:Q37"/>
+  <autoFilter ref="A4:Q61"/>
   <dataValidations count="1">
-    <dataValidation sqref="N5:N37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick from the list, or type your own note in the next column." prompt="Choose one." type="list" errorStyle="warning">
+    <dataValidation sqref="N5:N61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick from the list, or type your own note in the next column." prompt="Choose one." type="list" errorStyle="warning">
       <formula1>"Agree with recommendation,Different answer - see next column,Needs discussion"</formula1>
     </dataValidation>
   </dataValidations>

--- a/MVP-1/SRS/FlatWire_ClientQuestions.xlsx
+++ b/MVP-1/SRS/FlatWire_ClientQuestions.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Questions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions to Confirm'!$A$4:$L$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions to Confirm'!$A$4:$L$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Open Questions'!$A$4:$Q$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Issued August 12, 2026 · 57 open questions · 25 recorded decisions to confirm</t>
+          <t>Issued August 12, 2026 · 57 open questions · 27 recorded decisions to confirm</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -767,7 +767,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>25 decisions already taken, written back for your confirmation. Please complete the shaded columns.</t>
+          <t>27 decisions already taken, written back for your confirmation. Please complete the shaded columns.</t>
         </is>
       </c>
     </row>
@@ -3439,10 +3439,124 @@
       <c r="K29" s="8" t="n"/>
       <c r="L29" s="8" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Q88</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Output and packaging</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>A coil cut across a weld comes from two rods, and you asked for two identities to be kept rather than one. Your planning sheet writes those as the segment name with a letter added — R00002AA and R00001CA. Do you need that exact form, or two identities generated the normal way?</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>The form in the sheet cannot be used as a stored identifier. The letter it adds says which cut of the spool a piece came from, not which coil came from that rod, so every piece in one cut gets the same letter — which is why your own run contains R00004AB with no R00004AA. The same string can also mean two different things, and past twenty-six pieces off one rod it repeats outright. Generated identities avoid all three, and they are checked for uniqueness against every coil in the plant, which a locally built string is not.</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Two identities, generated the same way every other coil identity in the plant is generated — one rooted on each contributing rod. The label and the certificate show both, joined the way your sheet joins identities. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>The strings will not match the ones in your sheet</t>
+          </r>
+          <r>
+            <t>, and that is the visible consequence of this decision.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>Aug 26, 2026</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Confirm as recorded. If the exact strings from the sheet matter for continuity with something we have not seen, tell us — it is the one part of this we would revisit.</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
+      <c r="L30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Q89</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Output and packaging</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>For a coil made from two rods, should each rod's share appear as its own coil record in the wider plant systems, each carrying only its own weight?</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Roughly nine of the twenty-three spools on your own planning run carry a weld, so this is the normal case rather than an edge one. Recording each rod separately means cost, yield and the coil family tree all see the true split. The alternative credits the whole coil to one rod — on a 900 lb coil that means crediting 900 lb to a rod that supplied 500.</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>One record per contributing rod, each carrying its own weight — 500 lb against one rod and 400 lb against the other for a 900 lb coil, so the two add to the coil's weight and nothing is counted twice. Every rod is named on the certificate either way; this decides what the plant's own coil records show.</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Aug 26, 2026</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Two consequences need your sign-off. This changes how a skid counts its two coils, because a coil now has more than one record — the rule stays two coils per skid, counted as physical coils. And it is bound up with </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Q87</t>
+          </r>
+          <r>
+            <t>, the label question deferred on the 24 August call.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Confirm as recorded. It is the only option where cost and yield see the real numbers, and it removes a known mismatch between the coil family tree and the certificate. It costs more to build, which is why we are asking rather than assuming.</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="n"/>
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="8" t="n"/>
+      <c r="L31" s="8" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L29"/>
+  <autoFilter ref="A4:L31"/>
   <dataValidations count="1">
-    <dataValidation sqref="I5:I29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick from the list, or type your own note in the next column." prompt="Choose one." type="list" errorStyle="warning">
+    <dataValidation sqref="I5:I31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick from the list, or type your own note in the next column." prompt="Choose one." type="list" errorStyle="warning">
       <formula1>"Confirmed,Not confirmed - see next column,Needs discussion"</formula1>
     </dataValidation>
   </dataValidations>
